--- a/working/completed/API_Testing/src/test/java/resources/Data/complete_Loan_test_cases.xlsx
+++ b/working/completed/API_Testing/src/test/java/resources/Data/complete_Loan_test_cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohan S Naik\Pictures\working\completed\API_Testing\src\test\java\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A22A3C-4151-4C12-8052-9A71079552EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E61C81ED-1DF3-4024-A7B2-0EA4C9C44AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="1252">
   <si>
     <t>Horizon Bank</t>
   </si>
@@ -3409,6 +3411,12 @@
     <t>Occupation</t>
   </si>
   <si>
+    <t>payment_amount</t>
+  </si>
+  <si>
+    <t>installments_to_pay</t>
+  </si>
+  <si>
     <t>existing_liabilities</t>
   </si>
   <si>
@@ -3427,6 +3435,9 @@
     <t>Expected_Message</t>
   </si>
   <si>
+    <t>Foreclose_Account_ID</t>
+  </si>
+  <si>
     <t>TC_001</t>
   </si>
   <si>
@@ -3448,6 +3459,9 @@
     <t>Tester</t>
   </si>
   <si>
+    <t>8ff94733-5e1f-4db5-bcaf-d5247221d069</t>
+  </si>
+  <si>
     <t>Loan approved and disbursed successfully.</t>
   </si>
   <si>
@@ -3493,30 +3507,30 @@
     <t>Home Loan Minimum Amount</t>
   </si>
   <si>
+    <t>TC_007</t>
+  </si>
+  <si>
+    <t>Home Loan Maximum Amount</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>Home Loan Zero Amount</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>Home Loan Positive Amount</t>
+  </si>
+  <si>
     <t>Loan approved</t>
   </si>
   <si>
-    <t>TC_007</t>
-  </si>
-  <si>
-    <t>Home Loan Maximum Amount</t>
-  </si>
-  <si>
-    <t>TC_008</t>
-  </si>
-  <si>
-    <t>Home Loan Zero Amount</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>TC_009</t>
-  </si>
-  <si>
-    <t>Home Loan Positive Amount</t>
-  </si>
-  <si>
     <t>TC_010</t>
   </si>
   <si>
@@ -3637,21 +3651,24 @@
     <t>Home Loan Zero Tenure</t>
   </si>
   <si>
+    <t>Tenure (in months) must be a valid positive integer</t>
+  </si>
+  <si>
+    <t>TC_029</t>
+  </si>
+  <si>
+    <t>Home Loan Positive Tenure</t>
+  </si>
+  <si>
+    <t>TC_030</t>
+  </si>
+  <si>
+    <t>Home Loan Negative Tenure</t>
+  </si>
+  <si>
     <t>tenure</t>
   </si>
   <si>
-    <t>TC_029</t>
-  </si>
-  <si>
-    <t>Home Loan Positive Tenure</t>
-  </si>
-  <si>
-    <t>TC_030</t>
-  </si>
-  <si>
-    <t>Home Loan Negative Tenure</t>
-  </si>
-  <si>
     <t>TC_031</t>
   </si>
   <si>
@@ -3790,6 +3807,207 @@
     <t>Education Loan Below Minimum Tenure</t>
   </si>
   <si>
+    <t>TC_054</t>
+  </si>
+  <si>
+    <t>Home Loan Below Minimum Amount</t>
+  </si>
+  <si>
+    <t>Minimum loan amount for Home Loan is ₹5,00,000</t>
+  </si>
+  <si>
+    <t>TC_055</t>
+  </si>
+  <si>
+    <t>Home Loan Above Maximum Amount</t>
+  </si>
+  <si>
+    <t>Maximum loan amount for Home Loan is ₹2,00,00,000.</t>
+  </si>
+  <si>
+    <t>TC_056</t>
+  </si>
+  <si>
+    <t>Vehicle Loan Above Maximum Amount</t>
+  </si>
+  <si>
+    <t>Maximum loan amount for Vehicle Loan is ₹50,00,000</t>
+  </si>
+  <si>
+    <t>TC_057</t>
+  </si>
+  <si>
+    <t>Vehicle Loan Below Minimum Amount</t>
+  </si>
+  <si>
+    <t>Minimum loan amount for Vehicle Loan is ₹1,00,000.</t>
+  </si>
+  <si>
+    <t>TC_058</t>
+  </si>
+  <si>
+    <t>Personal Loan Below Minimum Amount</t>
+  </si>
+  <si>
+    <t>Minimum loan amount for Personal Loan is ₹50,000.</t>
+  </si>
+  <si>
+    <t>TC_059</t>
+  </si>
+  <si>
+    <t>Personal Loan Above Maximum Amount</t>
+  </si>
+  <si>
+    <t>Maximum loan amount for Personal Loan is ₹20,00,000.</t>
+  </si>
+  <si>
+    <t>TC_060</t>
+  </si>
+  <si>
+    <t>Education Loan Below Minimum Amount</t>
+  </si>
+  <si>
+    <t>Minimum loan amount for Education Loan is ₹1,00,000.</t>
+  </si>
+  <si>
+    <t>TC_061</t>
+  </si>
+  <si>
+    <t>Education Loan Above Maximum Amount</t>
+  </si>
+  <si>
+    <t>Maximum loan amount for Education Loan is ₹75,00,000.</t>
+  </si>
+  <si>
+    <t>TC_062</t>
+  </si>
+  <si>
+    <t>Home Loan Decimal Amount</t>
+  </si>
+  <si>
+    <t>TC_063</t>
+  </si>
+  <si>
+    <t>Vehicle Loan Decimal Amount</t>
+  </si>
+  <si>
+    <t>TC_064</t>
+  </si>
+  <si>
+    <t>Personal Loan Decimal Amount</t>
+  </si>
+  <si>
+    <t>TC_065</t>
+  </si>
+  <si>
+    <t>Education Loan Decimal Amount</t>
+  </si>
+  <si>
+    <t>TC_PAY_EMI_001</t>
+  </si>
+  <si>
+    <t>Pay One EMI</t>
+  </si>
+  <si>
+    <t>/loans/payment</t>
+  </si>
+  <si>
+    <t>EMI payment processed successfully.</t>
+  </si>
+  <si>
+    <t>TC_PAY_EMI_002</t>
+  </si>
+  <si>
+    <t>Pay Advance EMI Installments</t>
+  </si>
+  <si>
+    <t>TC_PAY_EMI_003</t>
+  </si>
+  <si>
+    <t>Pay EMI Below EMI Amount</t>
+  </si>
+  <si>
+    <t>BELOW_EMI</t>
+  </si>
+  <si>
+    <t>TC_PAY_EMI_004</t>
+  </si>
+  <si>
+    <t>Pay EMI Negative Amount</t>
+  </si>
+  <si>
+    <t>NEGATIVE</t>
+  </si>
+  <si>
+    <t>Payment amount must be a valid positive number.</t>
+  </si>
+  <si>
+    <t>TC_PAY_EMI_005</t>
+  </si>
+  <si>
+    <t>Pay EMI Less Than Required Total</t>
+  </si>
+  <si>
+    <t>LESS_THAN_TOTAL</t>
+  </si>
+  <si>
+    <t>TC_PAY_EMI_006</t>
+  </si>
+  <si>
+    <t>Pay EMI More Than 12 Installments</t>
+  </si>
+  <si>
+    <t>installments_to_pay must be a whole number between 1 and 12</t>
+  </si>
+  <si>
+    <t>TC_FORE_001</t>
+  </si>
+  <si>
+    <t>Valid Foreclosure</t>
+  </si>
+  <si>
+    <t>/loans/foreclose</t>
+  </si>
+  <si>
+    <t>foreclose</t>
+  </si>
+  <si>
+    <t>TC_FORE_002_HOME</t>
+  </si>
+  <si>
+    <t>Create First Loan For Max Limit</t>
+  </si>
+  <si>
+    <t>TC_FORE_002_VEHICLE</t>
+  </si>
+  <si>
+    <t>Create Second Loan For Max Limit</t>
+  </si>
+  <si>
+    <t>TC_FORE_002_EDU</t>
+  </si>
+  <si>
+    <t>Create Third Loan For Max Limit</t>
+  </si>
+  <si>
+    <t>TC_FORE_002_PERSONAL</t>
+  </si>
+  <si>
+    <t>Fourth Loan After Max Limit</t>
+  </si>
+  <si>
+    <t>TC_FORE_003</t>
+  </si>
+  <si>
+    <t>Foreclose With Insufficient Balance</t>
+  </si>
+  <si>
+    <t>0aee044a-f537-4e44-967c-d2143b69f30e</t>
+  </si>
+  <si>
+    <t>Minimum balance violation.</t>
+  </si>
+  <si>
     <t>Defect id</t>
   </si>
   <si>
@@ -3851,205 +4069,13 @@
   </si>
   <si>
     <t>Total Number of defects logged</t>
-  </si>
-  <si>
-    <t>546fcd83-8afe-4f04-8640-fe1297d9496b</t>
-  </si>
-  <si>
-    <t>Tenure (in months) must be a valid positive integer</t>
-  </si>
-  <si>
-    <t>payment_amount</t>
-  </si>
-  <si>
-    <t>installments_to_pay</t>
-  </si>
-  <si>
-    <t>Pay One EMI</t>
-  </si>
-  <si>
-    <t>/loans/payment</t>
-  </si>
-  <si>
-    <t>NEGATIVE</t>
-  </si>
-  <si>
-    <t>TC_054</t>
-  </si>
-  <si>
-    <t>Home Loan Below Minimum Amount</t>
-  </si>
-  <si>
-    <t>TC_055</t>
-  </si>
-  <si>
-    <t>TC_056</t>
-  </si>
-  <si>
-    <t>Vehicle Loan Above Maximum Amount</t>
-  </si>
-  <si>
-    <t>Vehicle Loan Below Minimum Amount</t>
-  </si>
-  <si>
-    <t>TC_057</t>
-  </si>
-  <si>
-    <t>TC_058</t>
-  </si>
-  <si>
-    <t>TC_059</t>
-  </si>
-  <si>
-    <t>TC_060</t>
-  </si>
-  <si>
-    <t>Personal Loan Below Minimum Amount</t>
-  </si>
-  <si>
-    <t>Personal Loan Above Maximum Amount</t>
-  </si>
-  <si>
-    <t>Education Loan Below Minimum Amount</t>
-  </si>
-  <si>
-    <t>Education Loan Above Maximum Amount</t>
-  </si>
-  <si>
-    <t>TC_061</t>
-  </si>
-  <si>
-    <t>Minimum loan amount for Home Loan is ₹5,00,000</t>
-  </si>
-  <si>
-    <t>Home Loan Above Maximum Amount</t>
-  </si>
-  <si>
-    <t>Maximum loan amount for Home Loan is ₹2,00,00,000.</t>
-  </si>
-  <si>
-    <t>Maximum loan amount for Vehicle Loan is ₹50,00,000</t>
-  </si>
-  <si>
-    <t>Minimum loan amount for Vehicle Loan is ₹1,00,000.</t>
-  </si>
-  <si>
-    <t>Minimum loan amount for Personal Loan is ₹50,000.</t>
-  </si>
-  <si>
-    <t>Maximum loan amount for Personal Loan is ₹20,00,000.</t>
-  </si>
-  <si>
-    <t>Minimum loan amount for Education Loan is ₹1,00,000.</t>
-  </si>
-  <si>
-    <t>Maximum loan amount for Education Loan is ₹75,00,000.</t>
-  </si>
-  <si>
-    <t>TC_FORE_001</t>
-  </si>
-  <si>
-    <t>/loans/foreclose</t>
-  </si>
-  <si>
-    <t>foreclose</t>
-  </si>
-  <si>
-    <t>TC_FORE_002_HOME</t>
-  </si>
-  <si>
-    <t>TC_FORE_002_VEHICLE</t>
-  </si>
-  <si>
-    <t>TC_FORE_002_EDU</t>
-  </si>
-  <si>
-    <t>TC_FORE_003</t>
-  </si>
-  <si>
-    <t>Valid Foreclosure</t>
-  </si>
-  <si>
-    <t>Create First Loan For Max Limit</t>
-  </si>
-  <si>
-    <t>Create Second Loan For Max Limit</t>
-  </si>
-  <si>
-    <t>Create Third Loan For Max Limit</t>
-  </si>
-  <si>
-    <t>TC_FORE_002_PERSONAL</t>
-  </si>
-  <si>
-    <t>Fourth Loan After Max Limit</t>
-  </si>
-  <si>
-    <t>Foreclose With Insufficient Balance</t>
-  </si>
-  <si>
-    <t>Minimum balance violation.</t>
-  </si>
-  <si>
-    <t>TC_PAY_EMI_001</t>
-  </si>
-  <si>
-    <t>TC_PAY_EMI_002</t>
-  </si>
-  <si>
-    <t>Pay Advance EMI Installments</t>
-  </si>
-  <si>
-    <t>TC_PAY_EMI_003</t>
-  </si>
-  <si>
-    <t>Pay EMI Below EMI Amount</t>
-  </si>
-  <si>
-    <t>BELOW_EMI</t>
-  </si>
-  <si>
-    <t>TC_PAY_EMI_004</t>
-  </si>
-  <si>
-    <t>Pay EMI Negative Amount</t>
-  </si>
-  <si>
-    <t>TC_PAY_EMI_005</t>
-  </si>
-  <si>
-    <t>Pay EMI Less Than Required Total</t>
-  </si>
-  <si>
-    <t>LESS_THAN_TOTAL</t>
-  </si>
-  <si>
-    <t>TC_PAY_EMI_006</t>
-  </si>
-  <si>
-    <t>Pay EMI More Than 12 Installments</t>
-  </si>
-  <si>
-    <t>installments_to_pay must be a whole number between 1 and 12</t>
-  </si>
-  <si>
-    <t>EMI payment processed successfully.</t>
-  </si>
-  <si>
-    <t>Payment amount must be a valid positive number.</t>
-  </si>
-  <si>
-    <t>a8ab272b-c611-47bb-935c-59751e0b39d1</t>
-  </si>
-  <si>
-    <t>Foreclose_Account_ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4708,21 +4734,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E66"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" customWidth="1"/>
     <col min="2" max="2" width="24" style="8" customWidth="1"/>
     <col min="3" max="3" width="62" style="8" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:5" ht="24.95" customHeight="1">
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
@@ -4739,7 +4765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="32" t="s">
         <v>6</v>
       </c>
@@ -4752,7 +4778,7 @@
       <c r="D3" s="34"/>
       <c r="E3" s="34"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="32" t="s">
         <v>6</v>
       </c>
@@ -4765,7 +4791,7 @@
       <c r="D4" s="34"/>
       <c r="E4" s="34"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="32" t="s">
         <v>6</v>
       </c>
@@ -4778,7 +4804,7 @@
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="32" t="s">
         <v>6</v>
       </c>
@@ -4791,7 +4817,7 @@
       <c r="D6" s="34"/>
       <c r="E6" s="34"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="32" t="s">
         <v>6</v>
       </c>
@@ -4804,7 +4830,7 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="32" t="s">
         <v>6</v>
       </c>
@@ -4817,7 +4843,7 @@
       <c r="D8" s="34"/>
       <c r="E8" s="34"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="32" t="s">
         <v>6</v>
       </c>
@@ -4830,7 +4856,7 @@
       <c r="D9" s="34"/>
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="32" t="s">
         <v>6</v>
       </c>
@@ -4843,7 +4869,7 @@
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="32" t="s">
         <v>6</v>
       </c>
@@ -4856,7 +4882,7 @@
       <c r="D11" s="34"/>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="32" t="s">
         <v>6</v>
       </c>
@@ -4869,7 +4895,7 @@
       <c r="D12" s="34"/>
       <c r="E12" s="34"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="32" t="s">
         <v>6</v>
       </c>
@@ -4882,7 +4908,7 @@
       <c r="D13" s="34"/>
       <c r="E13" s="34"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="32" t="s">
         <v>6</v>
       </c>
@@ -4895,7 +4921,7 @@
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="32" t="s">
         <v>6</v>
       </c>
@@ -4906,7 +4932,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="32" t="s">
         <v>6</v>
       </c>
@@ -4917,7 +4943,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="32" t="s">
         <v>6</v>
       </c>
@@ -4928,7 +4954,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="32" t="s">
         <v>6</v>
       </c>
@@ -4939,7 +4965,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="32" t="s">
         <v>6</v>
       </c>
@@ -4950,7 +4976,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="32" t="s">
         <v>6</v>
       </c>
@@ -4961,7 +4987,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="32" t="s">
         <v>6</v>
       </c>
@@ -4972,7 +4998,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="35" t="s">
         <v>6</v>
       </c>
@@ -4987,7 +5013,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="14" t="s">
         <v>6</v>
       </c>
@@ -5002,7 +5028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="14" t="s">
         <v>6</v>
       </c>
@@ -5017,7 +5043,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="14" t="s">
         <v>6</v>
       </c>
@@ -5032,7 +5058,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="14" t="s">
         <v>6</v>
       </c>
@@ -5047,7 +5073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="14" t="s">
         <v>6</v>
       </c>
@@ -5062,7 +5088,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="14" t="s">
         <v>6</v>
       </c>
@@ -5077,7 +5103,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="14" t="s">
         <v>6</v>
       </c>
@@ -5092,7 +5118,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="14" t="s">
         <v>6</v>
       </c>
@@ -5107,7 +5133,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="14" t="s">
         <v>6</v>
       </c>
@@ -5122,7 +5148,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="14" t="s">
         <v>6</v>
       </c>
@@ -5137,7 +5163,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="14" t="s">
         <v>6</v>
       </c>
@@ -5152,7 +5178,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="28.9">
       <c r="A34" s="14" t="s">
         <v>6</v>
       </c>
@@ -5167,7 +5193,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="14" t="s">
         <v>6</v>
       </c>
@@ -5182,7 +5208,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="14" t="s">
         <v>6</v>
       </c>
@@ -5197,7 +5223,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="14" t="s">
         <v>6</v>
       </c>
@@ -5212,7 +5238,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="14" t="s">
         <v>6</v>
       </c>
@@ -5227,7 +5253,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="14" t="s">
         <v>6</v>
       </c>
@@ -5242,7 +5268,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="14" t="s">
         <v>6</v>
       </c>
@@ -5257,7 +5283,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="14" t="s">
         <v>6</v>
       </c>
@@ -5272,7 +5298,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="14" t="s">
         <v>6</v>
       </c>
@@ -5287,7 +5313,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="14" t="s">
         <v>6</v>
       </c>
@@ -5302,7 +5328,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="14" t="s">
         <v>6</v>
       </c>
@@ -5317,7 +5343,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="14" t="s">
         <v>6</v>
       </c>
@@ -5332,7 +5358,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" s="14" t="s">
         <v>6</v>
       </c>
@@ -5347,7 +5373,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" s="14" t="s">
         <v>6</v>
       </c>
@@ -5362,7 +5388,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48" s="14" t="s">
         <v>6</v>
       </c>
@@ -5377,7 +5403,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" s="14" t="s">
         <v>6</v>
       </c>
@@ -5392,7 +5418,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" s="14" t="s">
         <v>6</v>
       </c>
@@ -5407,7 +5433,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" s="14" t="s">
         <v>6</v>
       </c>
@@ -5422,7 +5448,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" s="14" t="s">
         <v>6</v>
       </c>
@@ -5437,7 +5463,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53" s="14" t="s">
         <v>6</v>
       </c>
@@ -5452,7 +5478,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" s="14" t="s">
         <v>6</v>
       </c>
@@ -5467,7 +5493,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55" s="14" t="s">
         <v>6</v>
       </c>
@@ -5482,7 +5508,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56" s="14" t="s">
         <v>6</v>
       </c>
@@ -5497,7 +5523,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57" s="14" t="s">
         <v>6</v>
       </c>
@@ -5512,7 +5538,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58" s="14" t="s">
         <v>6</v>
       </c>
@@ -5527,7 +5553,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59" s="14" t="s">
         <v>6</v>
       </c>
@@ -5542,7 +5568,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" s="14" t="s">
         <v>6</v>
       </c>
@@ -5557,7 +5583,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="28.9">
       <c r="A61" s="14" t="s">
         <v>6</v>
       </c>
@@ -5572,7 +5598,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62" s="14" t="s">
         <v>6</v>
       </c>
@@ -5587,7 +5613,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63" s="14" t="s">
         <v>6</v>
       </c>
@@ -5602,7 +5628,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="28.9">
       <c r="A64" s="14" t="s">
         <v>6</v>
       </c>
@@ -5617,7 +5643,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65" s="14" t="s">
         <v>6</v>
       </c>
@@ -5632,7 +5658,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="28.9">
       <c r="A66" s="14" t="s">
         <v>6</v>
       </c>
@@ -5655,23 +5681,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:Q242"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="8" customWidth="1"/>
     <col min="5" max="5" width="38" style="8" customWidth="1"/>
     <col min="6" max="6" width="42" style="8" customWidth="1"/>
     <col min="7" max="7" width="38" style="8" customWidth="1"/>
     <col min="8" max="8" width="42" style="8" customWidth="1"/>
     <col min="9" max="9" width="59" style="8" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" style="8" customWidth="1"/>
-    <col min="11" max="11" width="7.44140625" style="8" customWidth="1"/>
-    <col min="12" max="17" width="9.109375" style="8"/>
+    <col min="10" max="10" width="12.85546875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" style="8" customWidth="1"/>
+    <col min="12" max="17" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1">
       <c r="A2" s="36" t="s">
         <v>180</v>
       </c>
@@ -5712,7 +5738,7 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1">
       <c r="A3" s="36">
         <f>ROW()-2</f>
         <v>1</v>
@@ -5752,7 +5778,7 @@
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="72">
       <c r="A4" s="36">
         <f t="shared" ref="A4:A67" si="0">ROW()-2</f>
         <v>2</v>
@@ -5792,7 +5818,7 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
     </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="72">
       <c r="A5" s="36">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -5832,7 +5858,7 @@
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="72">
       <c r="A6" s="36">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5872,7 +5898,7 @@
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="28.9">
       <c r="A7" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -5910,7 +5936,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="72">
       <c r="A8" s="36">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5950,7 +5976,7 @@
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="4" customFormat="1" ht="72">
       <c r="A9" s="36">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5990,7 +6016,7 @@
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
     </row>
-    <row r="10" spans="1:17" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="4" customFormat="1" ht="43.15">
       <c r="A10" s="36">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -6030,7 +6056,7 @@
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="4" customFormat="1" ht="28.9">
       <c r="A11" s="36">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -6070,7 +6096,7 @@
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
     </row>
-    <row r="12" spans="1:17" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="4" customFormat="1" ht="28.9">
       <c r="A12" s="36">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -6110,7 +6136,7 @@
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="4" customFormat="1" ht="28.9">
       <c r="A13" s="36">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -6150,7 +6176,7 @@
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
     </row>
-    <row r="14" spans="1:17" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="4" customFormat="1" ht="43.15">
       <c r="A14" s="36">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -6190,7 +6216,7 @@
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="4" customFormat="1" ht="28.9">
       <c r="A15" s="36">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -6230,7 +6256,7 @@
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
-    <row r="16" spans="1:17" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="4" customFormat="1" ht="28.9">
       <c r="A16" s="36">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -6270,7 +6296,7 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="4" customFormat="1" ht="28.9">
       <c r="A17" s="36">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -6310,7 +6336,7 @@
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="57.6">
       <c r="A18" s="36">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -6350,7 +6376,7 @@
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="4" customFormat="1" ht="43.15">
       <c r="A19" s="36">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -6390,7 +6416,7 @@
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
     </row>
-    <row r="20" spans="1:17" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="6" customFormat="1" ht="43.15">
       <c r="A20" s="36">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -6430,7 +6456,7 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
     </row>
-    <row r="21" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="28.9">
       <c r="A21" s="36">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -6464,7 +6490,7 @@
       </c>
       <c r="K21" s="38"/>
     </row>
-    <row r="22" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="28.9">
       <c r="A22" s="36">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -6498,7 +6524,7 @@
       </c>
       <c r="K22" s="38"/>
     </row>
-    <row r="23" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="28.9">
       <c r="A23" s="36">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6530,7 +6556,7 @@
       </c>
       <c r="K23" s="38"/>
     </row>
-    <row r="24" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="28.9">
       <c r="A24" s="36">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6564,7 +6590,7 @@
       </c>
       <c r="K24" s="38"/>
     </row>
-    <row r="25" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="43.15">
       <c r="A25" s="36">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -6598,7 +6624,7 @@
       </c>
       <c r="K25" s="38"/>
     </row>
-    <row r="26" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="28.9">
       <c r="A26" s="36">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -6632,7 +6658,7 @@
       </c>
       <c r="K26" s="38"/>
     </row>
-    <row r="27" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="28.9">
       <c r="A27" s="36">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6666,7 +6692,7 @@
       </c>
       <c r="K27" s="38"/>
     </row>
-    <row r="28" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="28.9">
       <c r="A28" s="36">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -6700,7 +6726,7 @@
       </c>
       <c r="K28" s="38"/>
     </row>
-    <row r="29" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="28.9">
       <c r="A29" s="36">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -6734,7 +6760,7 @@
       </c>
       <c r="K29" s="38"/>
     </row>
-    <row r="30" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="28.9">
       <c r="A30" s="36">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -6768,7 +6794,7 @@
       </c>
       <c r="K30" s="38"/>
     </row>
-    <row r="31" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="28.9">
       <c r="A31" s="36">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6802,7 +6828,7 @@
       </c>
       <c r="K31" s="38"/>
     </row>
-    <row r="32" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="28.9">
       <c r="A32" s="36">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6836,7 +6862,7 @@
       </c>
       <c r="K32" s="38"/>
     </row>
-    <row r="33" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="28.9">
       <c r="A33" s="36">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -6870,7 +6896,7 @@
       </c>
       <c r="K33" s="38"/>
     </row>
-    <row r="34" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="28.9">
       <c r="A34" s="36">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6904,7 +6930,7 @@
       </c>
       <c r="K34" s="38"/>
     </row>
-    <row r="35" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="28.9">
       <c r="A35" s="36">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -6939,7 +6965,7 @@
       <c r="K35" s="40"/>
       <c r="L35"/>
     </row>
-    <row r="36" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="28.9">
       <c r="A36" s="36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -6974,7 +7000,7 @@
       <c r="K36" s="40"/>
       <c r="L36"/>
     </row>
-    <row r="37" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="43.15">
       <c r="A37" s="36">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -7009,7 +7035,7 @@
       <c r="K37" s="40"/>
       <c r="L37"/>
     </row>
-    <row r="38" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="28.9">
       <c r="A38" s="36">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -7044,7 +7070,7 @@
       <c r="K38" s="40"/>
       <c r="L38"/>
     </row>
-    <row r="39" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="28.9">
       <c r="A39" s="36">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -7079,7 +7105,7 @@
       <c r="K39" s="40"/>
       <c r="L39"/>
     </row>
-    <row r="40" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="28.9">
       <c r="A40" s="36">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -7114,7 +7140,7 @@
       <c r="K40" s="40"/>
       <c r="L40"/>
     </row>
-    <row r="41" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="28.9">
       <c r="A41" s="36">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -7149,7 +7175,7 @@
       <c r="K41" s="40"/>
       <c r="L41"/>
     </row>
-    <row r="42" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="28.9">
       <c r="A42" s="36">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -7184,7 +7210,7 @@
       <c r="K42" s="40"/>
       <c r="L42"/>
     </row>
-    <row r="43" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="28.9">
       <c r="A43" s="36">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -7219,7 +7245,7 @@
       <c r="K43" s="40"/>
       <c r="L43"/>
     </row>
-    <row r="44" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="28.9">
       <c r="A44" s="36">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -7254,7 +7280,7 @@
       <c r="K44" s="40"/>
       <c r="L44"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12">
       <c r="A45" s="36">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -7289,7 +7315,7 @@
       <c r="K45" s="40"/>
       <c r="L45"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12">
       <c r="A46" s="36">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -7324,7 +7350,7 @@
       <c r="K46" s="40"/>
       <c r="L46"/>
     </row>
-    <row r="47" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="28.9">
       <c r="A47" s="36">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -7359,7 +7385,7 @@
       <c r="K47" s="40"/>
       <c r="L47"/>
     </row>
-    <row r="48" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="28.9">
       <c r="A48" s="36">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -7394,7 +7420,7 @@
       <c r="K48" s="10"/>
       <c r="L48"/>
     </row>
-    <row r="49" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="28.9">
       <c r="A49" s="36">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -7429,7 +7455,7 @@
       <c r="K49" s="10"/>
       <c r="L49"/>
     </row>
-    <row r="50" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="28.9">
       <c r="A50" s="36">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -7464,7 +7490,7 @@
       <c r="K50" s="10"/>
       <c r="L50"/>
     </row>
-    <row r="51" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="28.9">
       <c r="A51" s="36">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -7499,7 +7525,7 @@
       <c r="K51" s="10"/>
       <c r="L51"/>
     </row>
-    <row r="52" spans="1:12" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" s="16" customFormat="1" ht="57.6">
       <c r="A52" s="36">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -7533,7 +7559,7 @@
       </c>
       <c r="K52" s="15"/>
     </row>
-    <row r="53" spans="1:12" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" s="16" customFormat="1" ht="57.6">
       <c r="A53" s="36">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -7567,7 +7593,7 @@
       </c>
       <c r="K53" s="15"/>
     </row>
-    <row r="54" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" s="16" customFormat="1" ht="43.15">
       <c r="A54" s="36">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -7601,7 +7627,7 @@
       </c>
       <c r="K54" s="15"/>
     </row>
-    <row r="55" spans="1:12" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" s="16" customFormat="1" ht="43.15">
       <c r="A55" s="36">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -7635,7 +7661,7 @@
       </c>
       <c r="K55" s="15"/>
     </row>
-    <row r="56" spans="1:12" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" s="16" customFormat="1" ht="57.6">
       <c r="A56" s="36">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -7669,7 +7695,7 @@
       </c>
       <c r="K56" s="15"/>
     </row>
-    <row r="57" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="43.15">
       <c r="A57" s="36">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -7703,7 +7729,7 @@
       </c>
       <c r="K57" s="10"/>
     </row>
-    <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="43.15">
       <c r="A58" s="36">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -7737,7 +7763,7 @@
       </c>
       <c r="K58" s="10"/>
     </row>
-    <row r="59" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="43.15">
       <c r="A59" s="36">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -7771,7 +7797,7 @@
       </c>
       <c r="K59" s="10"/>
     </row>
-    <row r="60" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="43.15">
       <c r="A60" s="36">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -7805,7 +7831,7 @@
       </c>
       <c r="K60" s="10"/>
     </row>
-    <row r="61" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="43.15">
       <c r="A61" s="36">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -7839,7 +7865,7 @@
       </c>
       <c r="K61" s="10"/>
     </row>
-    <row r="62" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="43.15">
       <c r="A62" s="36">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -7873,7 +7899,7 @@
       </c>
       <c r="K62" s="10"/>
     </row>
-    <row r="63" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="72">
       <c r="A63" s="36">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -7908,7 +7934,7 @@
       <c r="K63" s="10"/>
       <c r="L63"/>
     </row>
-    <row r="64" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="43.15">
       <c r="A64" s="36">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -7943,7 +7969,7 @@
       <c r="K64" s="10"/>
       <c r="L64"/>
     </row>
-    <row r="65" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="43.15">
       <c r="A65" s="36">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -7978,7 +8004,7 @@
       <c r="K65" s="10"/>
       <c r="L65"/>
     </row>
-    <row r="66" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="43.15">
       <c r="A66" s="36">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -8013,7 +8039,7 @@
       <c r="K66" s="10"/>
       <c r="L66"/>
     </row>
-    <row r="67" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="43.15">
       <c r="A67" s="36">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -8048,7 +8074,7 @@
       <c r="K67" s="10"/>
       <c r="L67"/>
     </row>
-    <row r="68" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="43.15">
       <c r="A68" s="36">
         <f t="shared" ref="A68:A99" si="1">ROW()-2</f>
         <v>66</v>
@@ -8083,7 +8109,7 @@
       <c r="K68" s="10"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:12" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" s="4" customFormat="1" ht="43.15">
       <c r="A69" s="36">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -8117,7 +8143,7 @@
       </c>
       <c r="K69" s="10"/>
     </row>
-    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="43.15">
       <c r="A70" s="36">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -8151,7 +8177,7 @@
       </c>
       <c r="K70" s="10"/>
     </row>
-    <row r="71" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="43.15">
       <c r="A71" s="36">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -8185,7 +8211,7 @@
       </c>
       <c r="K71" s="10"/>
     </row>
-    <row r="72" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="57.6">
       <c r="A72" s="36">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -8219,7 +8245,7 @@
       </c>
       <c r="K72" s="10"/>
     </row>
-    <row r="73" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="57.6">
       <c r="A73" s="36">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -8253,7 +8279,7 @@
       </c>
       <c r="K73" s="10"/>
     </row>
-    <row r="74" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="57.6">
       <c r="A74" s="36">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -8287,7 +8313,7 @@
       </c>
       <c r="K74" s="10"/>
     </row>
-    <row r="75" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="43.15">
       <c r="A75" s="36">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -8321,7 +8347,7 @@
       </c>
       <c r="K75" s="10"/>
     </row>
-    <row r="76" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="57.6">
       <c r="A76" s="36">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -8355,7 +8381,7 @@
       </c>
       <c r="K76" s="10"/>
     </row>
-    <row r="77" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="57.6">
       <c r="A77" s="36">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -8389,7 +8415,7 @@
       </c>
       <c r="K77" s="10"/>
     </row>
-    <row r="78" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="72">
       <c r="A78" s="36">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -8423,7 +8449,7 @@
       </c>
       <c r="K78" s="10"/>
     </row>
-    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="43.15">
       <c r="A79" s="36">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -8457,7 +8483,7 @@
       </c>
       <c r="K79" s="10"/>
     </row>
-    <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="43.15">
       <c r="A80" s="36">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -8491,7 +8517,7 @@
       </c>
       <c r="K80" s="10"/>
     </row>
-    <row r="81" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="43.15">
       <c r="A81" s="36">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -8525,7 +8551,7 @@
       </c>
       <c r="K81" s="10"/>
     </row>
-    <row r="82" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="43.15">
       <c r="A82" s="36">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -8559,7 +8585,7 @@
       </c>
       <c r="K82" s="10"/>
     </row>
-    <row r="83" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="43.15">
       <c r="A83" s="36">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -8593,7 +8619,7 @@
       </c>
       <c r="K83" s="10"/>
     </row>
-    <row r="84" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="43.15">
       <c r="A84" s="36">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -8627,7 +8653,7 @@
       </c>
       <c r="K84" s="10"/>
     </row>
-    <row r="85" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" ht="57.6">
       <c r="A85" s="36">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -8661,7 +8687,7 @@
       </c>
       <c r="K85" s="10"/>
     </row>
-    <row r="86" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" ht="57.6">
       <c r="A86" s="36">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -8695,7 +8721,7 @@
       </c>
       <c r="K86" s="10"/>
     </row>
-    <row r="87" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" ht="43.15">
       <c r="A87" s="29">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -8729,7 +8755,7 @@
       </c>
       <c r="K87" s="10"/>
     </row>
-    <row r="88" spans="1:17" s="26" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" s="26" customFormat="1" ht="57.6">
       <c r="A88" s="29">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -8769,7 +8795,7 @@
       <c r="P88" s="25"/>
       <c r="Q88" s="25"/>
     </row>
-    <row r="89" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A89" s="29">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -8809,7 +8835,7 @@
       <c r="P89" s="25"/>
       <c r="Q89" s="25"/>
     </row>
-    <row r="90" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A90" s="29">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -8849,7 +8875,7 @@
       <c r="P90" s="25"/>
       <c r="Q90" s="25"/>
     </row>
-    <row r="91" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A91" s="29">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -8889,7 +8915,7 @@
       <c r="P91" s="25"/>
       <c r="Q91" s="25"/>
     </row>
-    <row r="92" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A92" s="29">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -8929,7 +8955,7 @@
       <c r="P92" s="25"/>
       <c r="Q92" s="25"/>
     </row>
-    <row r="93" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A93" s="29">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -8969,7 +8995,7 @@
       <c r="P93" s="25"/>
       <c r="Q93" s="25"/>
     </row>
-    <row r="94" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A94" s="29">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -9009,7 +9035,7 @@
       <c r="P94" s="25"/>
       <c r="Q94" s="25"/>
     </row>
-    <row r="95" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A95" s="29">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -9049,7 +9075,7 @@
       <c r="P95" s="25"/>
       <c r="Q95" s="25"/>
     </row>
-    <row r="96" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A96" s="29">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -9089,7 +9115,7 @@
       <c r="P96" s="25"/>
       <c r="Q96" s="25"/>
     </row>
-    <row r="97" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A97" s="29">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -9129,7 +9155,7 @@
       <c r="P97" s="25"/>
       <c r="Q97" s="25"/>
     </row>
-    <row r="98" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A98" s="29">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -9169,7 +9195,7 @@
       <c r="P98" s="25"/>
       <c r="Q98" s="25"/>
     </row>
-    <row r="99" spans="1:17" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" s="26" customFormat="1" ht="28.9">
       <c r="A99" s="29">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -9209,7 +9235,7 @@
       <c r="P99" s="25"/>
       <c r="Q99" s="25"/>
     </row>
-    <row r="100" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" s="26" customFormat="1">
       <c r="A100" s="25"/>
       <c r="B100" s="25"/>
       <c r="C100" s="25"/>
@@ -9228,7 +9254,7 @@
       <c r="P100" s="25"/>
       <c r="Q100" s="25"/>
     </row>
-    <row r="101" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" s="26" customFormat="1">
       <c r="A101" s="25"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -9247,7 +9273,7 @@
       <c r="P101" s="25"/>
       <c r="Q101" s="25"/>
     </row>
-    <row r="102" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" s="26" customFormat="1">
       <c r="A102" s="25"/>
       <c r="B102" s="25"/>
       <c r="C102" s="25"/>
@@ -9266,7 +9292,7 @@
       <c r="P102" s="25"/>
       <c r="Q102" s="25"/>
     </row>
-    <row r="103" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" s="26" customFormat="1">
       <c r="A103" s="25"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -9285,7 +9311,7 @@
       <c r="P103" s="25"/>
       <c r="Q103" s="25"/>
     </row>
-    <row r="104" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" s="26" customFormat="1">
       <c r="A104" s="25"/>
       <c r="B104" s="25"/>
       <c r="C104" s="25"/>
@@ -9304,7 +9330,7 @@
       <c r="P104" s="25"/>
       <c r="Q104" s="25"/>
     </row>
-    <row r="105" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" s="26" customFormat="1">
       <c r="A105" s="25"/>
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
@@ -9323,7 +9349,7 @@
       <c r="P105" s="25"/>
       <c r="Q105" s="25"/>
     </row>
-    <row r="106" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" s="26" customFormat="1">
       <c r="A106" s="25"/>
       <c r="B106" s="25"/>
       <c r="C106" s="25"/>
@@ -9342,7 +9368,7 @@
       <c r="P106" s="25"/>
       <c r="Q106" s="25"/>
     </row>
-    <row r="107" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" s="26" customFormat="1">
       <c r="A107" s="27"/>
       <c r="B107" s="28"/>
       <c r="C107" s="28"/>
@@ -9361,7 +9387,7 @@
       <c r="P107" s="25"/>
       <c r="Q107" s="25"/>
     </row>
-    <row r="108" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" s="26" customFormat="1">
       <c r="A108" s="25"/>
       <c r="B108" s="25"/>
       <c r="C108" s="25"/>
@@ -9380,7 +9406,7 @@
       <c r="P108" s="25"/>
       <c r="Q108" s="25"/>
     </row>
-    <row r="109" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" s="26" customFormat="1">
       <c r="A109" s="25"/>
       <c r="B109" s="25"/>
       <c r="C109" s="25"/>
@@ -9399,7 +9425,7 @@
       <c r="P109" s="25"/>
       <c r="Q109" s="25"/>
     </row>
-    <row r="110" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" s="26" customFormat="1">
       <c r="A110" s="25"/>
       <c r="B110" s="25"/>
       <c r="C110" s="25"/>
@@ -9418,7 +9444,7 @@
       <c r="P110" s="25"/>
       <c r="Q110" s="25"/>
     </row>
-    <row r="111" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" s="26" customFormat="1">
       <c r="A111" s="25"/>
       <c r="B111" s="25"/>
       <c r="C111" s="25"/>
@@ -9437,7 +9463,7 @@
       <c r="P111" s="25"/>
       <c r="Q111" s="25"/>
     </row>
-    <row r="112" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" s="26" customFormat="1">
       <c r="A112" s="25"/>
       <c r="B112" s="25"/>
       <c r="C112" s="25"/>
@@ -9456,7 +9482,7 @@
       <c r="P112" s="25"/>
       <c r="Q112" s="25"/>
     </row>
-    <row r="113" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" s="26" customFormat="1">
       <c r="A113" s="25"/>
       <c r="B113" s="25"/>
       <c r="C113" s="25"/>
@@ -9475,7 +9501,7 @@
       <c r="P113" s="25"/>
       <c r="Q113" s="25"/>
     </row>
-    <row r="114" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" s="26" customFormat="1">
       <c r="A114" s="25"/>
       <c r="B114" s="25"/>
       <c r="C114" s="25"/>
@@ -9494,7 +9520,7 @@
       <c r="P114" s="25"/>
       <c r="Q114" s="25"/>
     </row>
-    <row r="115" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" s="26" customFormat="1">
       <c r="A115" s="25"/>
       <c r="B115" s="25"/>
       <c r="C115" s="25"/>
@@ -9513,7 +9539,7 @@
       <c r="P115" s="25"/>
       <c r="Q115" s="25"/>
     </row>
-    <row r="116" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" s="26" customFormat="1">
       <c r="A116" s="27"/>
       <c r="B116" s="28"/>
       <c r="C116" s="28"/>
@@ -9532,7 +9558,7 @@
       <c r="P116" s="25"/>
       <c r="Q116" s="25"/>
     </row>
-    <row r="117" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" s="26" customFormat="1">
       <c r="A117" s="25"/>
       <c r="B117" s="25"/>
       <c r="C117" s="25"/>
@@ -9551,7 +9577,7 @@
       <c r="P117" s="25"/>
       <c r="Q117" s="25"/>
     </row>
-    <row r="118" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" s="26" customFormat="1">
       <c r="A118" s="25"/>
       <c r="B118" s="25"/>
       <c r="C118" s="25"/>
@@ -9570,7 +9596,7 @@
       <c r="P118" s="25"/>
       <c r="Q118" s="25"/>
     </row>
-    <row r="119" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" s="26" customFormat="1">
       <c r="A119" s="25"/>
       <c r="B119" s="25"/>
       <c r="C119" s="25"/>
@@ -9589,7 +9615,7 @@
       <c r="P119" s="25"/>
       <c r="Q119" s="25"/>
     </row>
-    <row r="120" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" s="26" customFormat="1">
       <c r="A120" s="25"/>
       <c r="B120" s="25"/>
       <c r="C120" s="25"/>
@@ -9608,7 +9634,7 @@
       <c r="P120" s="25"/>
       <c r="Q120" s="25"/>
     </row>
-    <row r="121" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" s="26" customFormat="1">
       <c r="A121" s="25"/>
       <c r="B121" s="25"/>
       <c r="C121" s="25"/>
@@ -9627,7 +9653,7 @@
       <c r="P121" s="25"/>
       <c r="Q121" s="25"/>
     </row>
-    <row r="122" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" s="26" customFormat="1">
       <c r="A122" s="25"/>
       <c r="B122" s="25"/>
       <c r="C122" s="25"/>
@@ -9646,7 +9672,7 @@
       <c r="P122" s="25"/>
       <c r="Q122" s="25"/>
     </row>
-    <row r="123" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" s="26" customFormat="1">
       <c r="A123" s="25"/>
       <c r="B123" s="25"/>
       <c r="C123" s="25"/>
@@ -9665,7 +9691,7 @@
       <c r="P123" s="25"/>
       <c r="Q123" s="25"/>
     </row>
-    <row r="124" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" s="26" customFormat="1">
       <c r="A124" s="25"/>
       <c r="B124" s="25"/>
       <c r="C124" s="25"/>
@@ -9684,7 +9710,7 @@
       <c r="P124" s="25"/>
       <c r="Q124" s="25"/>
     </row>
-    <row r="125" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" s="26" customFormat="1">
       <c r="A125" s="25"/>
       <c r="B125" s="25"/>
       <c r="C125" s="25"/>
@@ -9703,7 +9729,7 @@
       <c r="P125" s="25"/>
       <c r="Q125" s="25"/>
     </row>
-    <row r="126" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" s="26" customFormat="1">
       <c r="A126" s="25"/>
       <c r="B126" s="25"/>
       <c r="C126" s="25"/>
@@ -9722,7 +9748,7 @@
       <c r="P126" s="25"/>
       <c r="Q126" s="25"/>
     </row>
-    <row r="127" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" s="26" customFormat="1">
       <c r="A127" s="25"/>
       <c r="B127" s="25"/>
       <c r="C127" s="25"/>
@@ -9741,7 +9767,7 @@
       <c r="P127" s="25"/>
       <c r="Q127" s="25"/>
     </row>
-    <row r="128" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" s="26" customFormat="1">
       <c r="A128" s="25"/>
       <c r="B128" s="25"/>
       <c r="C128" s="25"/>
@@ -9760,7 +9786,7 @@
       <c r="P128" s="25"/>
       <c r="Q128" s="25"/>
     </row>
-    <row r="129" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" s="26" customFormat="1">
       <c r="A129" s="25"/>
       <c r="B129" s="25"/>
       <c r="C129" s="25"/>
@@ -9779,7 +9805,7 @@
       <c r="P129" s="25"/>
       <c r="Q129" s="25"/>
     </row>
-    <row r="130" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" s="26" customFormat="1">
       <c r="A130" s="25"/>
       <c r="B130" s="25"/>
       <c r="C130" s="25"/>
@@ -9798,7 +9824,7 @@
       <c r="P130" s="25"/>
       <c r="Q130" s="25"/>
     </row>
-    <row r="131" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" s="26" customFormat="1">
       <c r="A131" s="25"/>
       <c r="B131" s="25"/>
       <c r="C131" s="25"/>
@@ -9817,7 +9843,7 @@
       <c r="P131" s="25"/>
       <c r="Q131" s="25"/>
     </row>
-    <row r="132" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" s="26" customFormat="1">
       <c r="A132" s="25"/>
       <c r="B132" s="25"/>
       <c r="C132" s="25"/>
@@ -9836,7 +9862,7 @@
       <c r="P132" s="25"/>
       <c r="Q132" s="25"/>
     </row>
-    <row r="133" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" s="26" customFormat="1">
       <c r="A133" s="25"/>
       <c r="B133" s="25"/>
       <c r="C133" s="25"/>
@@ -9855,7 +9881,7 @@
       <c r="P133" s="25"/>
       <c r="Q133" s="25"/>
     </row>
-    <row r="134" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" s="26" customFormat="1">
       <c r="A134" s="25"/>
       <c r="B134" s="25"/>
       <c r="C134" s="25"/>
@@ -9874,7 +9900,7 @@
       <c r="P134" s="25"/>
       <c r="Q134" s="25"/>
     </row>
-    <row r="135" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" s="26" customFormat="1">
       <c r="A135" s="25"/>
       <c r="B135" s="25"/>
       <c r="C135" s="25"/>
@@ -9893,7 +9919,7 @@
       <c r="P135" s="25"/>
       <c r="Q135" s="25"/>
     </row>
-    <row r="136" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" s="26" customFormat="1">
       <c r="A136" s="25"/>
       <c r="B136" s="25"/>
       <c r="C136" s="25"/>
@@ -9912,7 +9938,7 @@
       <c r="P136" s="25"/>
       <c r="Q136" s="25"/>
     </row>
-    <row r="137" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" s="26" customFormat="1">
       <c r="A137" s="25"/>
       <c r="B137" s="25"/>
       <c r="C137" s="25"/>
@@ -9931,7 +9957,7 @@
       <c r="P137" s="25"/>
       <c r="Q137" s="25"/>
     </row>
-    <row r="138" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" s="26" customFormat="1">
       <c r="A138" s="25"/>
       <c r="B138" s="25"/>
       <c r="C138" s="25"/>
@@ -9950,7 +9976,7 @@
       <c r="P138" s="25"/>
       <c r="Q138" s="25"/>
     </row>
-    <row r="139" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" s="26" customFormat="1">
       <c r="A139" s="25"/>
       <c r="B139" s="25"/>
       <c r="C139" s="25"/>
@@ -9969,7 +9995,7 @@
       <c r="P139" s="25"/>
       <c r="Q139" s="25"/>
     </row>
-    <row r="140" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" s="26" customFormat="1">
       <c r="A140" s="25"/>
       <c r="B140" s="25"/>
       <c r="C140" s="25"/>
@@ -9988,7 +10014,7 @@
       <c r="P140" s="25"/>
       <c r="Q140" s="25"/>
     </row>
-    <row r="141" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" s="26" customFormat="1">
       <c r="A141" s="25"/>
       <c r="B141" s="25"/>
       <c r="C141" s="25"/>
@@ -10007,7 +10033,7 @@
       <c r="P141" s="25"/>
       <c r="Q141" s="25"/>
     </row>
-    <row r="142" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" s="26" customFormat="1">
       <c r="A142" s="25"/>
       <c r="B142" s="25"/>
       <c r="C142" s="25"/>
@@ -10026,7 +10052,7 @@
       <c r="P142" s="25"/>
       <c r="Q142" s="25"/>
     </row>
-    <row r="143" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" s="26" customFormat="1">
       <c r="A143" s="25"/>
       <c r="B143" s="25"/>
       <c r="C143" s="25"/>
@@ -10045,7 +10071,7 @@
       <c r="P143" s="25"/>
       <c r="Q143" s="25"/>
     </row>
-    <row r="144" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" s="26" customFormat="1">
       <c r="A144" s="25"/>
       <c r="B144" s="25"/>
       <c r="C144" s="25"/>
@@ -10064,7 +10090,7 @@
       <c r="P144" s="25"/>
       <c r="Q144" s="25"/>
     </row>
-    <row r="145" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" s="26" customFormat="1">
       <c r="A145" s="25"/>
       <c r="B145" s="25"/>
       <c r="C145" s="25"/>
@@ -10083,7 +10109,7 @@
       <c r="P145" s="25"/>
       <c r="Q145" s="25"/>
     </row>
-    <row r="146" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" s="26" customFormat="1">
       <c r="A146" s="25"/>
       <c r="B146" s="25"/>
       <c r="C146" s="25"/>
@@ -10102,7 +10128,7 @@
       <c r="P146" s="25"/>
       <c r="Q146" s="25"/>
     </row>
-    <row r="147" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" s="26" customFormat="1">
       <c r="A147" s="25"/>
       <c r="B147" s="25"/>
       <c r="C147" s="25"/>
@@ -10121,7 +10147,7 @@
       <c r="P147" s="25"/>
       <c r="Q147" s="25"/>
     </row>
-    <row r="148" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" s="26" customFormat="1">
       <c r="A148" s="25"/>
       <c r="B148" s="25"/>
       <c r="C148" s="25"/>
@@ -10140,7 +10166,7 @@
       <c r="P148" s="25"/>
       <c r="Q148" s="25"/>
     </row>
-    <row r="149" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" s="26" customFormat="1">
       <c r="A149" s="25"/>
       <c r="B149" s="25"/>
       <c r="C149" s="25"/>
@@ -10159,7 +10185,7 @@
       <c r="P149" s="25"/>
       <c r="Q149" s="25"/>
     </row>
-    <row r="150" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" s="26" customFormat="1">
       <c r="A150" s="25"/>
       <c r="B150" s="25"/>
       <c r="C150" s="25"/>
@@ -10178,7 +10204,7 @@
       <c r="P150" s="25"/>
       <c r="Q150" s="25"/>
     </row>
-    <row r="151" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" s="26" customFormat="1">
       <c r="A151" s="25"/>
       <c r="B151" s="25"/>
       <c r="C151" s="25"/>
@@ -10197,7 +10223,7 @@
       <c r="P151" s="25"/>
       <c r="Q151" s="25"/>
     </row>
-    <row r="152" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" s="26" customFormat="1">
       <c r="A152" s="25"/>
       <c r="B152" s="25"/>
       <c r="C152" s="25"/>
@@ -10216,7 +10242,7 @@
       <c r="P152" s="25"/>
       <c r="Q152" s="25"/>
     </row>
-    <row r="153" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" s="26" customFormat="1">
       <c r="A153" s="25"/>
       <c r="B153" s="25"/>
       <c r="C153" s="25"/>
@@ -10235,7 +10261,7 @@
       <c r="P153" s="25"/>
       <c r="Q153" s="25"/>
     </row>
-    <row r="154" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" s="26" customFormat="1">
       <c r="A154" s="25"/>
       <c r="B154" s="25"/>
       <c r="C154" s="25"/>
@@ -10254,7 +10280,7 @@
       <c r="P154" s="25"/>
       <c r="Q154" s="25"/>
     </row>
-    <row r="155" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" s="26" customFormat="1">
       <c r="A155" s="25"/>
       <c r="B155" s="25"/>
       <c r="C155" s="25"/>
@@ -10273,7 +10299,7 @@
       <c r="P155" s="25"/>
       <c r="Q155" s="25"/>
     </row>
-    <row r="156" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" s="26" customFormat="1">
       <c r="A156" s="25"/>
       <c r="B156" s="25"/>
       <c r="C156" s="25"/>
@@ -10292,7 +10318,7 @@
       <c r="P156" s="25"/>
       <c r="Q156" s="25"/>
     </row>
-    <row r="157" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" s="26" customFormat="1">
       <c r="A157" s="25"/>
       <c r="B157" s="25"/>
       <c r="C157" s="25"/>
@@ -10311,7 +10337,7 @@
       <c r="P157" s="25"/>
       <c r="Q157" s="25"/>
     </row>
-    <row r="158" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" s="26" customFormat="1">
       <c r="A158" s="25"/>
       <c r="B158" s="25"/>
       <c r="C158" s="25"/>
@@ -10330,7 +10356,7 @@
       <c r="P158" s="25"/>
       <c r="Q158" s="25"/>
     </row>
-    <row r="159" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" s="26" customFormat="1">
       <c r="A159" s="25"/>
       <c r="B159" s="25"/>
       <c r="C159" s="25"/>
@@ -10349,7 +10375,7 @@
       <c r="P159" s="25"/>
       <c r="Q159" s="25"/>
     </row>
-    <row r="160" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" s="26" customFormat="1">
       <c r="A160" s="25"/>
       <c r="B160" s="25"/>
       <c r="C160" s="25"/>
@@ -10368,7 +10394,7 @@
       <c r="P160" s="25"/>
       <c r="Q160" s="25"/>
     </row>
-    <row r="161" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" s="26" customFormat="1">
       <c r="A161" s="25"/>
       <c r="B161" s="25"/>
       <c r="C161" s="25"/>
@@ -10387,7 +10413,7 @@
       <c r="P161" s="25"/>
       <c r="Q161" s="25"/>
     </row>
-    <row r="162" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" s="26" customFormat="1">
       <c r="A162" s="25"/>
       <c r="B162" s="25"/>
       <c r="C162" s="25"/>
@@ -10406,7 +10432,7 @@
       <c r="P162" s="25"/>
       <c r="Q162" s="25"/>
     </row>
-    <row r="163" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" s="26" customFormat="1">
       <c r="A163" s="25"/>
       <c r="B163" s="25"/>
       <c r="C163" s="25"/>
@@ -10425,7 +10451,7 @@
       <c r="P163" s="25"/>
       <c r="Q163" s="25"/>
     </row>
-    <row r="164" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" s="26" customFormat="1">
       <c r="A164" s="25"/>
       <c r="B164" s="25"/>
       <c r="C164" s="25"/>
@@ -10444,7 +10470,7 @@
       <c r="P164" s="25"/>
       <c r="Q164" s="25"/>
     </row>
-    <row r="165" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" s="26" customFormat="1">
       <c r="A165" s="25"/>
       <c r="B165" s="25"/>
       <c r="C165" s="25"/>
@@ -10463,7 +10489,7 @@
       <c r="P165" s="25"/>
       <c r="Q165" s="25"/>
     </row>
-    <row r="166" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" s="26" customFormat="1">
       <c r="A166" s="25"/>
       <c r="B166" s="25"/>
       <c r="C166" s="25"/>
@@ -10482,7 +10508,7 @@
       <c r="P166" s="25"/>
       <c r="Q166" s="25"/>
     </row>
-    <row r="167" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" s="26" customFormat="1">
       <c r="A167" s="25"/>
       <c r="B167" s="25"/>
       <c r="C167" s="25"/>
@@ -10501,7 +10527,7 @@
       <c r="P167" s="25"/>
       <c r="Q167" s="25"/>
     </row>
-    <row r="168" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" s="26" customFormat="1">
       <c r="A168" s="25"/>
       <c r="B168" s="25"/>
       <c r="C168" s="25"/>
@@ -10520,7 +10546,7 @@
       <c r="P168" s="25"/>
       <c r="Q168" s="25"/>
     </row>
-    <row r="169" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" s="26" customFormat="1">
       <c r="A169" s="25"/>
       <c r="B169" s="25"/>
       <c r="C169" s="25"/>
@@ -10539,7 +10565,7 @@
       <c r="P169" s="25"/>
       <c r="Q169" s="25"/>
     </row>
-    <row r="170" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" s="26" customFormat="1">
       <c r="A170" s="25"/>
       <c r="B170" s="25"/>
       <c r="C170" s="25"/>
@@ -10558,7 +10584,7 @@
       <c r="P170" s="25"/>
       <c r="Q170" s="25"/>
     </row>
-    <row r="171" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" s="26" customFormat="1">
       <c r="A171" s="25"/>
       <c r="B171" s="25"/>
       <c r="C171" s="25"/>
@@ -10577,7 +10603,7 @@
       <c r="P171" s="25"/>
       <c r="Q171" s="25"/>
     </row>
-    <row r="172" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" s="26" customFormat="1">
       <c r="A172" s="25"/>
       <c r="B172" s="25"/>
       <c r="C172" s="25"/>
@@ -10596,7 +10622,7 @@
       <c r="P172" s="25"/>
       <c r="Q172" s="25"/>
     </row>
-    <row r="173" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" s="26" customFormat="1">
       <c r="A173" s="25"/>
       <c r="B173" s="25"/>
       <c r="C173" s="25"/>
@@ -10615,7 +10641,7 @@
       <c r="P173" s="25"/>
       <c r="Q173" s="25"/>
     </row>
-    <row r="174" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" s="26" customFormat="1">
       <c r="A174" s="25"/>
       <c r="B174" s="25"/>
       <c r="C174" s="25"/>
@@ -10634,7 +10660,7 @@
       <c r="P174" s="25"/>
       <c r="Q174" s="25"/>
     </row>
-    <row r="175" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" s="26" customFormat="1">
       <c r="A175" s="25"/>
       <c r="B175" s="25"/>
       <c r="C175" s="25"/>
@@ -10653,7 +10679,7 @@
       <c r="P175" s="25"/>
       <c r="Q175" s="25"/>
     </row>
-    <row r="176" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" s="26" customFormat="1">
       <c r="A176" s="25"/>
       <c r="B176" s="25"/>
       <c r="C176" s="25"/>
@@ -10672,7 +10698,7 @@
       <c r="P176" s="25"/>
       <c r="Q176" s="25"/>
     </row>
-    <row r="177" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" s="26" customFormat="1">
       <c r="A177" s="25"/>
       <c r="B177" s="25"/>
       <c r="C177" s="25"/>
@@ -10691,7 +10717,7 @@
       <c r="P177" s="25"/>
       <c r="Q177" s="25"/>
     </row>
-    <row r="178" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" s="26" customFormat="1">
       <c r="A178" s="25"/>
       <c r="B178" s="25"/>
       <c r="C178" s="25"/>
@@ -10710,7 +10736,7 @@
       <c r="P178" s="25"/>
       <c r="Q178" s="25"/>
     </row>
-    <row r="179" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" s="26" customFormat="1">
       <c r="A179" s="25"/>
       <c r="B179" s="25"/>
       <c r="C179" s="25"/>
@@ -10729,7 +10755,7 @@
       <c r="P179" s="25"/>
       <c r="Q179" s="25"/>
     </row>
-    <row r="180" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" s="26" customFormat="1">
       <c r="A180" s="25"/>
       <c r="B180" s="25"/>
       <c r="C180" s="25"/>
@@ -10748,7 +10774,7 @@
       <c r="P180" s="25"/>
       <c r="Q180" s="25"/>
     </row>
-    <row r="181" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" s="26" customFormat="1">
       <c r="A181" s="25"/>
       <c r="B181" s="25"/>
       <c r="C181" s="25"/>
@@ -10767,7 +10793,7 @@
       <c r="P181" s="25"/>
       <c r="Q181" s="25"/>
     </row>
-    <row r="182" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" s="26" customFormat="1">
       <c r="A182" s="25"/>
       <c r="B182" s="25"/>
       <c r="C182" s="25"/>
@@ -10786,7 +10812,7 @@
       <c r="P182" s="25"/>
       <c r="Q182" s="25"/>
     </row>
-    <row r="183" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" s="26" customFormat="1">
       <c r="A183" s="25"/>
       <c r="B183" s="25"/>
       <c r="C183" s="25"/>
@@ -10805,7 +10831,7 @@
       <c r="P183" s="25"/>
       <c r="Q183" s="25"/>
     </row>
-    <row r="184" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" s="26" customFormat="1">
       <c r="A184" s="25"/>
       <c r="B184" s="25"/>
       <c r="C184" s="25"/>
@@ -10824,7 +10850,7 @@
       <c r="P184" s="25"/>
       <c r="Q184" s="25"/>
     </row>
-    <row r="185" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" s="26" customFormat="1">
       <c r="A185" s="25"/>
       <c r="B185" s="25"/>
       <c r="C185" s="25"/>
@@ -10843,7 +10869,7 @@
       <c r="P185" s="25"/>
       <c r="Q185" s="25"/>
     </row>
-    <row r="186" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" s="26" customFormat="1">
       <c r="A186" s="25"/>
       <c r="B186" s="25"/>
       <c r="C186" s="25"/>
@@ -10862,7 +10888,7 @@
       <c r="P186" s="25"/>
       <c r="Q186" s="25"/>
     </row>
-    <row r="187" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" s="26" customFormat="1">
       <c r="A187" s="25"/>
       <c r="B187" s="25"/>
       <c r="C187" s="25"/>
@@ -10881,7 +10907,7 @@
       <c r="P187" s="25"/>
       <c r="Q187" s="25"/>
     </row>
-    <row r="188" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" s="26" customFormat="1">
       <c r="A188" s="25"/>
       <c r="B188" s="25"/>
       <c r="C188" s="25"/>
@@ -10900,7 +10926,7 @@
       <c r="P188" s="25"/>
       <c r="Q188" s="25"/>
     </row>
-    <row r="189" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" s="26" customFormat="1">
       <c r="A189" s="25"/>
       <c r="B189" s="25"/>
       <c r="C189" s="25"/>
@@ -10919,7 +10945,7 @@
       <c r="P189" s="25"/>
       <c r="Q189" s="25"/>
     </row>
-    <row r="190" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" s="26" customFormat="1">
       <c r="A190" s="25"/>
       <c r="B190" s="25"/>
       <c r="C190" s="25"/>
@@ -10938,7 +10964,7 @@
       <c r="P190" s="25"/>
       <c r="Q190" s="25"/>
     </row>
-    <row r="191" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" s="26" customFormat="1">
       <c r="A191" s="25"/>
       <c r="B191" s="25"/>
       <c r="C191" s="25"/>
@@ -10957,7 +10983,7 @@
       <c r="P191" s="25"/>
       <c r="Q191" s="25"/>
     </row>
-    <row r="192" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" s="26" customFormat="1">
       <c r="A192" s="25"/>
       <c r="B192" s="25"/>
       <c r="C192" s="25"/>
@@ -10976,7 +11002,7 @@
       <c r="P192" s="25"/>
       <c r="Q192" s="25"/>
     </row>
-    <row r="193" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" s="26" customFormat="1">
       <c r="A193" s="25"/>
       <c r="B193" s="25"/>
       <c r="C193" s="25"/>
@@ -10995,7 +11021,7 @@
       <c r="P193" s="25"/>
       <c r="Q193" s="25"/>
     </row>
-    <row r="194" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" s="26" customFormat="1">
       <c r="A194" s="25"/>
       <c r="B194" s="25"/>
       <c r="C194" s="25"/>
@@ -11014,7 +11040,7 @@
       <c r="P194" s="25"/>
       <c r="Q194" s="25"/>
     </row>
-    <row r="195" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" s="26" customFormat="1">
       <c r="A195" s="25"/>
       <c r="B195" s="25"/>
       <c r="C195" s="25"/>
@@ -11033,7 +11059,7 @@
       <c r="P195" s="25"/>
       <c r="Q195" s="25"/>
     </row>
-    <row r="196" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" s="26" customFormat="1">
       <c r="A196" s="25"/>
       <c r="B196" s="25"/>
       <c r="C196" s="25"/>
@@ -11052,7 +11078,7 @@
       <c r="P196" s="25"/>
       <c r="Q196" s="25"/>
     </row>
-    <row r="197" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" s="26" customFormat="1">
       <c r="A197" s="25"/>
       <c r="B197" s="25"/>
       <c r="C197" s="25"/>
@@ -11071,7 +11097,7 @@
       <c r="P197" s="25"/>
       <c r="Q197" s="25"/>
     </row>
-    <row r="198" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" s="26" customFormat="1">
       <c r="A198" s="25"/>
       <c r="B198" s="25"/>
       <c r="C198" s="25"/>
@@ -11090,7 +11116,7 @@
       <c r="P198" s="25"/>
       <c r="Q198" s="25"/>
     </row>
-    <row r="199" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" s="26" customFormat="1">
       <c r="A199" s="25"/>
       <c r="B199" s="25"/>
       <c r="C199" s="25"/>
@@ -11109,7 +11135,7 @@
       <c r="P199" s="25"/>
       <c r="Q199" s="25"/>
     </row>
-    <row r="200" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" s="26" customFormat="1">
       <c r="A200" s="25"/>
       <c r="B200" s="25"/>
       <c r="C200" s="25"/>
@@ -11128,7 +11154,7 @@
       <c r="P200" s="25"/>
       <c r="Q200" s="25"/>
     </row>
-    <row r="201" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" s="26" customFormat="1">
       <c r="A201" s="25"/>
       <c r="B201" s="25"/>
       <c r="C201" s="25"/>
@@ -11147,7 +11173,7 @@
       <c r="P201" s="25"/>
       <c r="Q201" s="25"/>
     </row>
-    <row r="202" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" s="26" customFormat="1">
       <c r="A202" s="25"/>
       <c r="B202" s="25"/>
       <c r="C202" s="25"/>
@@ -11166,7 +11192,7 @@
       <c r="P202" s="25"/>
       <c r="Q202" s="25"/>
     </row>
-    <row r="203" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" s="26" customFormat="1">
       <c r="A203" s="25"/>
       <c r="B203" s="25"/>
       <c r="C203" s="25"/>
@@ -11185,7 +11211,7 @@
       <c r="P203" s="25"/>
       <c r="Q203" s="25"/>
     </row>
-    <row r="204" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" s="26" customFormat="1">
       <c r="A204" s="25"/>
       <c r="B204" s="25"/>
       <c r="C204" s="25"/>
@@ -11204,7 +11230,7 @@
       <c r="P204" s="25"/>
       <c r="Q204" s="25"/>
     </row>
-    <row r="205" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" s="26" customFormat="1">
       <c r="A205" s="25"/>
       <c r="B205" s="25"/>
       <c r="C205" s="25"/>
@@ -11223,7 +11249,7 @@
       <c r="P205" s="25"/>
       <c r="Q205" s="25"/>
     </row>
-    <row r="206" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" s="26" customFormat="1">
       <c r="A206" s="25"/>
       <c r="B206" s="25"/>
       <c r="C206" s="25"/>
@@ -11242,7 +11268,7 @@
       <c r="P206" s="25"/>
       <c r="Q206" s="25"/>
     </row>
-    <row r="207" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" s="26" customFormat="1">
       <c r="A207" s="25"/>
       <c r="B207" s="25"/>
       <c r="C207" s="25"/>
@@ -11261,7 +11287,7 @@
       <c r="P207" s="25"/>
       <c r="Q207" s="25"/>
     </row>
-    <row r="208" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" s="26" customFormat="1">
       <c r="A208" s="25"/>
       <c r="B208" s="25"/>
       <c r="C208" s="25"/>
@@ -11280,7 +11306,7 @@
       <c r="P208" s="25"/>
       <c r="Q208" s="25"/>
     </row>
-    <row r="209" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" s="26" customFormat="1">
       <c r="A209" s="25"/>
       <c r="B209" s="25"/>
       <c r="C209" s="25"/>
@@ -11299,7 +11325,7 @@
       <c r="P209" s="25"/>
       <c r="Q209" s="25"/>
     </row>
-    <row r="210" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" s="26" customFormat="1">
       <c r="A210" s="25"/>
       <c r="B210" s="25"/>
       <c r="C210" s="25"/>
@@ -11318,7 +11344,7 @@
       <c r="P210" s="25"/>
       <c r="Q210" s="25"/>
     </row>
-    <row r="211" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" s="26" customFormat="1">
       <c r="A211" s="25"/>
       <c r="B211" s="25"/>
       <c r="C211" s="25"/>
@@ -11337,7 +11363,7 @@
       <c r="P211" s="25"/>
       <c r="Q211" s="25"/>
     </row>
-    <row r="212" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" s="26" customFormat="1">
       <c r="A212" s="25"/>
       <c r="B212" s="25"/>
       <c r="C212" s="25"/>
@@ -11356,7 +11382,7 @@
       <c r="P212" s="25"/>
       <c r="Q212" s="25"/>
     </row>
-    <row r="213" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" s="26" customFormat="1">
       <c r="A213" s="25"/>
       <c r="B213" s="25"/>
       <c r="C213" s="25"/>
@@ -11375,7 +11401,7 @@
       <c r="P213" s="25"/>
       <c r="Q213" s="25"/>
     </row>
-    <row r="214" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" s="26" customFormat="1">
       <c r="A214" s="25"/>
       <c r="B214" s="25"/>
       <c r="C214" s="25"/>
@@ -11394,7 +11420,7 @@
       <c r="P214" s="25"/>
       <c r="Q214" s="25"/>
     </row>
-    <row r="215" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" s="26" customFormat="1">
       <c r="A215" s="25"/>
       <c r="B215" s="25"/>
       <c r="C215" s="25"/>
@@ -11413,7 +11439,7 @@
       <c r="P215" s="25"/>
       <c r="Q215" s="25"/>
     </row>
-    <row r="216" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" s="26" customFormat="1">
       <c r="A216" s="25"/>
       <c r="B216" s="25"/>
       <c r="C216" s="25"/>
@@ -11432,7 +11458,7 @@
       <c r="P216" s="25"/>
       <c r="Q216" s="25"/>
     </row>
-    <row r="217" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" s="26" customFormat="1">
       <c r="A217" s="25"/>
       <c r="B217" s="25"/>
       <c r="C217" s="25"/>
@@ -11451,7 +11477,7 @@
       <c r="P217" s="25"/>
       <c r="Q217" s="25"/>
     </row>
-    <row r="218" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" s="26" customFormat="1">
       <c r="A218" s="25"/>
       <c r="B218" s="25"/>
       <c r="C218" s="25"/>
@@ -11470,7 +11496,7 @@
       <c r="P218" s="25"/>
       <c r="Q218" s="25"/>
     </row>
-    <row r="219" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:17" s="26" customFormat="1">
       <c r="A219" s="25"/>
       <c r="B219" s="25"/>
       <c r="C219" s="25"/>
@@ -11489,7 +11515,7 @@
       <c r="P219" s="25"/>
       <c r="Q219" s="25"/>
     </row>
-    <row r="220" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" s="26" customFormat="1">
       <c r="A220" s="25"/>
       <c r="B220" s="25"/>
       <c r="C220" s="25"/>
@@ -11508,7 +11534,7 @@
       <c r="P220" s="25"/>
       <c r="Q220" s="25"/>
     </row>
-    <row r="221" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" s="26" customFormat="1">
       <c r="A221" s="25"/>
       <c r="B221" s="25"/>
       <c r="C221" s="25"/>
@@ -11527,7 +11553,7 @@
       <c r="P221" s="25"/>
       <c r="Q221" s="25"/>
     </row>
-    <row r="222" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" s="26" customFormat="1">
       <c r="A222" s="25"/>
       <c r="B222" s="25"/>
       <c r="C222" s="25"/>
@@ -11546,7 +11572,7 @@
       <c r="P222" s="25"/>
       <c r="Q222" s="25"/>
     </row>
-    <row r="223" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" s="26" customFormat="1">
       <c r="A223" s="25"/>
       <c r="B223" s="25"/>
       <c r="C223" s="25"/>
@@ -11565,7 +11591,7 @@
       <c r="P223" s="25"/>
       <c r="Q223" s="25"/>
     </row>
-    <row r="224" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" s="26" customFormat="1">
       <c r="A224" s="25"/>
       <c r="B224" s="25"/>
       <c r="C224" s="25"/>
@@ -11584,7 +11610,7 @@
       <c r="P224" s="25"/>
       <c r="Q224" s="25"/>
     </row>
-    <row r="225" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" s="26" customFormat="1">
       <c r="A225" s="25"/>
       <c r="B225" s="25"/>
       <c r="C225" s="25"/>
@@ -11603,7 +11629,7 @@
       <c r="P225" s="25"/>
       <c r="Q225" s="25"/>
     </row>
-    <row r="226" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" s="26" customFormat="1">
       <c r="A226" s="25"/>
       <c r="B226" s="25"/>
       <c r="C226" s="25"/>
@@ -11622,7 +11648,7 @@
       <c r="P226" s="25"/>
       <c r="Q226" s="25"/>
     </row>
-    <row r="227" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" s="26" customFormat="1">
       <c r="A227" s="25"/>
       <c r="B227" s="25"/>
       <c r="C227" s="25"/>
@@ -11641,7 +11667,7 @@
       <c r="P227" s="25"/>
       <c r="Q227" s="25"/>
     </row>
-    <row r="228" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" s="26" customFormat="1">
       <c r="A228" s="25"/>
       <c r="B228" s="25"/>
       <c r="C228" s="25"/>
@@ -11660,7 +11686,7 @@
       <c r="P228" s="25"/>
       <c r="Q228" s="25"/>
     </row>
-    <row r="229" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" s="26" customFormat="1">
       <c r="A229" s="25"/>
       <c r="B229" s="25"/>
       <c r="C229" s="25"/>
@@ -11679,7 +11705,7 @@
       <c r="P229" s="25"/>
       <c r="Q229" s="25"/>
     </row>
-    <row r="230" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" s="26" customFormat="1">
       <c r="A230" s="25"/>
       <c r="B230" s="25"/>
       <c r="C230" s="25"/>
@@ -11698,7 +11724,7 @@
       <c r="P230" s="25"/>
       <c r="Q230" s="25"/>
     </row>
-    <row r="231" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" s="26" customFormat="1">
       <c r="A231" s="25"/>
       <c r="B231" s="25"/>
       <c r="C231" s="25"/>
@@ -11717,7 +11743,7 @@
       <c r="P231" s="25"/>
       <c r="Q231" s="25"/>
     </row>
-    <row r="232" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" s="26" customFormat="1">
       <c r="A232" s="25"/>
       <c r="B232" s="25"/>
       <c r="C232" s="25"/>
@@ -11736,7 +11762,7 @@
       <c r="P232" s="25"/>
       <c r="Q232" s="25"/>
     </row>
-    <row r="233" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" s="26" customFormat="1">
       <c r="A233" s="25"/>
       <c r="B233" s="25"/>
       <c r="C233" s="25"/>
@@ -11755,7 +11781,7 @@
       <c r="P233" s="25"/>
       <c r="Q233" s="25"/>
     </row>
-    <row r="234" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" s="26" customFormat="1">
       <c r="A234" s="25"/>
       <c r="B234" s="25"/>
       <c r="C234" s="25"/>
@@ -11774,7 +11800,7 @@
       <c r="P234" s="25"/>
       <c r="Q234" s="25"/>
     </row>
-    <row r="235" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" s="26" customFormat="1">
       <c r="A235" s="25"/>
       <c r="B235" s="25"/>
       <c r="C235" s="25"/>
@@ -11793,7 +11819,7 @@
       <c r="P235" s="25"/>
       <c r="Q235" s="25"/>
     </row>
-    <row r="236" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" s="26" customFormat="1">
       <c r="A236" s="25"/>
       <c r="B236" s="25"/>
       <c r="C236" s="25"/>
@@ -11812,7 +11838,7 @@
       <c r="P236" s="25"/>
       <c r="Q236" s="25"/>
     </row>
-    <row r="237" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" s="26" customFormat="1">
       <c r="A237" s="25"/>
       <c r="B237" s="25"/>
       <c r="C237" s="25"/>
@@ -11831,7 +11857,7 @@
       <c r="P237" s="25"/>
       <c r="Q237" s="25"/>
     </row>
-    <row r="238" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" s="26" customFormat="1">
       <c r="A238" s="25"/>
       <c r="B238" s="25"/>
       <c r="C238" s="25"/>
@@ -11850,7 +11876,7 @@
       <c r="P238" s="25"/>
       <c r="Q238" s="25"/>
     </row>
-    <row r="239" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" s="26" customFormat="1">
       <c r="A239" s="25"/>
       <c r="B239" s="25"/>
       <c r="C239" s="25"/>
@@ -11869,7 +11895,7 @@
       <c r="P239" s="25"/>
       <c r="Q239" s="25"/>
     </row>
-    <row r="240" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" s="26" customFormat="1">
       <c r="A240" s="25"/>
       <c r="B240" s="25"/>
       <c r="C240" s="25"/>
@@ -11888,7 +11914,7 @@
       <c r="P240" s="25"/>
       <c r="Q240" s="25"/>
     </row>
-    <row r="241" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" s="26" customFormat="1">
       <c r="A241" s="25"/>
       <c r="B241" s="25"/>
       <c r="C241" s="25"/>
@@ -11907,7 +11933,7 @@
       <c r="P241" s="25"/>
       <c r="Q241" s="25"/>
     </row>
-    <row r="242" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" s="26" customFormat="1">
       <c r="A242" s="25"/>
       <c r="B242" s="25"/>
       <c r="C242" s="25"/>
@@ -11951,18 +11977,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29332D14-40E2-479F-8DC1-9652937770B0}">
   <dimension ref="A1:Q64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17">
       <c r="A1" s="36" t="s">
         <v>771</v>
       </c>
@@ -12003,7 +12029,7 @@
       <c r="P1" s="9"/>
       <c r="Q1" s="9"/>
     </row>
-    <row r="2" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="86.45">
       <c r="A2" s="59">
         <v>1</v>
       </c>
@@ -12037,7 +12063,7 @@
       <c r="K2" s="59"/>
       <c r="L2" s="60"/>
     </row>
-    <row r="3" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="57.6">
       <c r="A3" s="59">
         <v>2</v>
       </c>
@@ -12071,7 +12097,7 @@
       <c r="K3" s="59"/>
       <c r="L3" s="60"/>
     </row>
-    <row r="4" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="115.15">
       <c r="A4" s="59">
         <v>3</v>
       </c>
@@ -12105,7 +12131,7 @@
       <c r="K4" s="59"/>
       <c r="L4" s="60"/>
     </row>
-    <row r="5" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="86.45">
       <c r="A5" s="59">
         <v>4</v>
       </c>
@@ -12139,7 +12165,7 @@
       <c r="K5" s="59"/>
       <c r="L5" s="60"/>
     </row>
-    <row r="6" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="100.9">
       <c r="A6" s="59">
         <v>5</v>
       </c>
@@ -12173,7 +12199,7 @@
       <c r="K6" s="64"/>
       <c r="L6" s="16"/>
     </row>
-    <row r="7" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="86.45">
       <c r="A7" s="59">
         <v>6</v>
       </c>
@@ -12207,7 +12233,7 @@
       <c r="K7" s="59"/>
       <c r="L7" s="60"/>
     </row>
-    <row r="8" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="100.9">
       <c r="A8" s="59">
         <v>7</v>
       </c>
@@ -12241,7 +12267,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="16"/>
     </row>
-    <row r="9" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="86.45">
       <c r="A9" s="59">
         <v>8</v>
       </c>
@@ -12275,7 +12301,7 @@
       <c r="K9" s="19"/>
       <c r="L9" s="16"/>
     </row>
-    <row r="10" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="57.6">
       <c r="A10" s="59">
         <v>9</v>
       </c>
@@ -12309,7 +12335,7 @@
       <c r="K10" s="19"/>
       <c r="L10" s="16"/>
     </row>
-    <row r="11" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="86.45">
       <c r="A11" s="59">
         <v>10</v>
       </c>
@@ -12343,7 +12369,7 @@
       <c r="K11" s="19"/>
       <c r="L11" s="16"/>
     </row>
-    <row r="12" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="72">
       <c r="A12" s="59">
         <v>11</v>
       </c>
@@ -12377,7 +12403,7 @@
       <c r="K12" s="19"/>
       <c r="L12" s="16"/>
     </row>
-    <row r="13" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="86.45">
       <c r="A13" s="59">
         <v>12</v>
       </c>
@@ -12411,7 +12437,7 @@
       <c r="K13" s="19"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="72">
       <c r="A14" s="59">
         <v>13</v>
       </c>
@@ -12445,7 +12471,7 @@
       <c r="K14" s="19"/>
       <c r="L14" s="16"/>
     </row>
-    <row r="15" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="72">
       <c r="A15" s="59">
         <v>14</v>
       </c>
@@ -12479,7 +12505,7 @@
       <c r="K15" s="19"/>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="72">
       <c r="A16" s="59">
         <v>15</v>
       </c>
@@ -12513,7 +12539,7 @@
       <c r="K16" s="19"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="72">
       <c r="A17" s="59">
         <v>16</v>
       </c>
@@ -12547,7 +12573,7 @@
       <c r="K17" s="19"/>
       <c r="L17" s="16"/>
     </row>
-    <row r="18" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="72">
       <c r="A18" s="59">
         <v>17</v>
       </c>
@@ -12581,7 +12607,7 @@
       <c r="K18" s="19"/>
       <c r="L18" s="16"/>
     </row>
-    <row r="19" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="72">
       <c r="A19" s="59">
         <v>18</v>
       </c>
@@ -12615,7 +12641,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="16"/>
     </row>
-    <row r="20" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="72">
       <c r="A20" s="59">
         <v>19</v>
       </c>
@@ -12649,7 +12675,7 @@
       <c r="K20" s="19"/>
       <c r="L20" s="16"/>
     </row>
-    <row r="21" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="86.45">
       <c r="A21" s="59">
         <v>20</v>
       </c>
@@ -12683,7 +12709,7 @@
       <c r="K21" s="19"/>
       <c r="L21" s="16"/>
     </row>
-    <row r="22" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="57.6">
       <c r="A22" s="59">
         <v>21</v>
       </c>
@@ -12717,7 +12743,7 @@
       <c r="K22" s="19"/>
       <c r="L22" s="16"/>
     </row>
-    <row r="23" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="57.6">
       <c r="A23" s="59">
         <v>22</v>
       </c>
@@ -12751,7 +12777,7 @@
       <c r="K23" s="19"/>
       <c r="L23" s="16"/>
     </row>
-    <row r="24" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="57.6">
       <c r="A24" s="59">
         <v>23</v>
       </c>
@@ -12783,7 +12809,7 @@
       <c r="K24" s="19"/>
       <c r="L24" s="16"/>
     </row>
-    <row r="25" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="57.6">
       <c r="A25" s="59">
         <v>24</v>
       </c>
@@ -12815,7 +12841,7 @@
       <c r="K25" s="19"/>
       <c r="L25" s="16"/>
     </row>
-    <row r="26" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="72">
       <c r="A26" s="59">
         <v>25</v>
       </c>
@@ -12847,7 +12873,7 @@
       <c r="K26" s="19"/>
       <c r="L26" s="16"/>
     </row>
-    <row r="27" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="57.6">
       <c r="A27" s="59">
         <v>26</v>
       </c>
@@ -12879,7 +12905,7 @@
       <c r="K27" s="19"/>
       <c r="L27" s="16"/>
     </row>
-    <row r="28" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="43.15">
       <c r="A28" s="59">
         <v>27</v>
       </c>
@@ -12911,7 +12937,7 @@
       <c r="K28" s="19"/>
       <c r="L28" s="16"/>
     </row>
-    <row r="29" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="86.45">
       <c r="A29" s="59">
         <v>28</v>
       </c>
@@ -12941,7 +12967,7 @@
       <c r="K29" s="19"/>
       <c r="L29" s="16"/>
     </row>
-    <row r="30" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="86.45">
       <c r="A30" s="59">
         <v>29</v>
       </c>
@@ -12971,7 +12997,7 @@
       <c r="K30" s="19"/>
       <c r="L30" s="16"/>
     </row>
-    <row r="31" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="57.6">
       <c r="A31" s="59">
         <v>30</v>
       </c>
@@ -13001,7 +13027,7 @@
       <c r="K31" s="19"/>
       <c r="L31" s="16"/>
     </row>
-    <row r="32" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="72">
       <c r="A32" s="59">
         <v>31</v>
       </c>
@@ -13031,7 +13057,7 @@
       <c r="K32" s="19"/>
       <c r="L32" s="16"/>
     </row>
-    <row r="33" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="86.45">
       <c r="A33" s="59">
         <v>32</v>
       </c>
@@ -13061,7 +13087,7 @@
       <c r="K33" s="19"/>
       <c r="L33" s="16"/>
     </row>
-    <row r="34" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="100.9">
       <c r="A34" s="59">
         <v>33</v>
       </c>
@@ -13090,7 +13116,7 @@
       <c r="J34" s="19"/>
       <c r="K34" s="40"/>
     </row>
-    <row r="35" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="86.45">
       <c r="A35" s="59">
         <v>34</v>
       </c>
@@ -13119,7 +13145,7 @@
       <c r="J35" s="19"/>
       <c r="K35" s="40"/>
     </row>
-    <row r="36" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="100.9">
       <c r="A36" s="59">
         <v>35</v>
       </c>
@@ -13148,7 +13174,7 @@
       <c r="J36" s="19"/>
       <c r="K36" s="40"/>
     </row>
-    <row r="37" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="86.45">
       <c r="A37" s="59">
         <v>36</v>
       </c>
@@ -13177,7 +13203,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="40"/>
     </row>
-    <row r="38" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="57.6">
       <c r="A38" s="59">
         <v>37</v>
       </c>
@@ -13208,7 +13234,7 @@
       </c>
       <c r="K38" s="40"/>
     </row>
-    <row r="39" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="86.45">
       <c r="A39" s="59">
         <v>38</v>
       </c>
@@ -13237,7 +13263,7 @@
       <c r="J39" s="19"/>
       <c r="K39" s="40"/>
     </row>
-    <row r="40" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="86.45">
       <c r="A40" s="59">
         <v>39</v>
       </c>
@@ -13266,7 +13292,7 @@
       <c r="J40" s="19"/>
       <c r="K40" s="40"/>
     </row>
-    <row r="41" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="72">
       <c r="A41" s="59">
         <v>40</v>
       </c>
@@ -13295,7 +13321,7 @@
       <c r="J41" s="19"/>
       <c r="K41" s="40"/>
     </row>
-    <row r="42" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="57.6">
       <c r="A42" s="59">
         <v>41</v>
       </c>
@@ -13326,7 +13352,7 @@
       </c>
       <c r="K42" s="40"/>
     </row>
-    <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="43.15">
       <c r="A43" s="59">
         <v>42</v>
       </c>
@@ -13357,7 +13383,7 @@
       </c>
       <c r="K43" s="40"/>
     </row>
-    <row r="44" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="57.6">
       <c r="A44" s="59">
         <v>43</v>
       </c>
@@ -13388,7 +13414,7 @@
       </c>
       <c r="K44" s="40"/>
     </row>
-    <row r="45" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="57.6">
       <c r="A45" s="59">
         <v>44</v>
       </c>
@@ -13419,7 +13445,7 @@
       </c>
       <c r="K45" s="40"/>
     </row>
-    <row r="46" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="57.6">
       <c r="A46" s="59">
         <v>45</v>
       </c>
@@ -13450,109 +13476,109 @@
       </c>
       <c r="K46" s="40"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12">
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12">
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
     </row>
-    <row r="49" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:8">
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
     </row>
-    <row r="50" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="5:8">
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
     </row>
-    <row r="51" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="5:8">
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
     </row>
-    <row r="52" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="5:8">
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="5:8">
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
     </row>
-    <row r="54" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="5:8">
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
     </row>
-    <row r="55" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="5:8">
       <c r="E55" s="14"/>
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
     </row>
-    <row r="56" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="5:8">
       <c r="E56" s="14"/>
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
     </row>
-    <row r="57" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="5:8">
       <c r="E57" s="14"/>
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
     </row>
-    <row r="58" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="5:8">
       <c r="E58" s="14"/>
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
     </row>
-    <row r="59" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="5:8">
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
     </row>
-    <row r="60" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="5:8">
       <c r="E60" s="14"/>
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
     </row>
-    <row r="61" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="5:8">
       <c r="E61" s="14"/>
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
     </row>
-    <row r="62" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="5:8">
       <c r="E62" s="14"/>
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
     </row>
-    <row r="63" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="5:8">
       <c r="E63" s="14"/>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
     </row>
-    <row r="64" spans="5:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="5:8">
       <c r="E64" s="14"/>
       <c r="F64" s="14"/>
       <c r="G64" s="14"/>
@@ -13571,26 +13597,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF377F39-0639-4374-A411-0F9340D902D4}">
   <dimension ref="A1:S95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="36.33203125" customWidth="1"/>
-    <col min="13" max="13" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="36.28515625" customWidth="1"/>
+    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="70.28515625" customWidth="1"/>
+    <col min="19" max="19" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>1022</v>
       </c>
@@ -13622,51 +13648,51 @@
         <v>1031</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>1182</v>
+        <v>1032</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>1183</v>
+        <v>1033</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15">
       <c r="A2" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B2" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C2" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D2" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E2" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F2" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G2">
         <v>500000</v>
@@ -13678,13 +13704,13 @@
         <v>1200000</v>
       </c>
       <c r="J2" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P2">
         <v>201</v>
@@ -13693,27 +13719,27 @@
         <v>1</v>
       </c>
       <c r="R2" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15">
+      <c r="A3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E3" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="F3" t="s">
         <v>1046</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1043</v>
       </c>
       <c r="G3">
         <v>500000</v>
@@ -13725,13 +13751,13 @@
         <v>1200000</v>
       </c>
       <c r="J3" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="O3" s="14"/>
       <c r="P3">
@@ -13741,27 +13767,27 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15">
+      <c r="A4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>1042</v>
-      </c>
       <c r="F4" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G4">
         <v>300000</v>
@@ -13773,13 +13799,13 @@
         <v>900000</v>
       </c>
       <c r="J4" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M4">
         <v>5000</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4">
@@ -13789,27 +13815,27 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15">
+      <c r="A5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>1042</v>
-      </c>
       <c r="F5" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G5">
         <v>200000</v>
@@ -13821,13 +13847,13 @@
         <v>800000</v>
       </c>
       <c r="J5" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M5">
         <v>3000</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P5">
         <v>201</v>
@@ -13836,27 +13862,27 @@
         <v>1</v>
       </c>
       <c r="R5" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15">
+      <c r="A6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>1042</v>
-      </c>
       <c r="F6" s="14" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G6">
         <v>150000</v>
@@ -13868,13 +13894,13 @@
         <v>10000000</v>
       </c>
       <c r="J6" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M6">
         <v>2000</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P6">
         <v>500</v>
@@ -13883,27 +13909,27 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15">
       <c r="A7" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C7" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D7" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G7">
         <v>500000</v>
@@ -13915,13 +13941,13 @@
         <v>1200000</v>
       </c>
       <c r="J7" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P7">
         <v>201</v>
@@ -13930,27 +13956,27 @@
         <v>1</v>
       </c>
       <c r="R7" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15">
+      <c r="A8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>1042</v>
-      </c>
       <c r="F8" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G8">
         <v>20000000</v>
@@ -13962,13 +13988,13 @@
         <v>12000000</v>
       </c>
       <c r="J8" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P8">
         <v>201</v>
@@ -13977,27 +14003,27 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15">
+      <c r="A9" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>1042</v>
-      </c>
       <c r="F9" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -14009,13 +14035,13 @@
         <v>1200000</v>
       </c>
       <c r="J9" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P9">
         <v>400</v>
@@ -14024,27 +14050,27 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15">
       <c r="A10" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="C10" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D10" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G10">
         <v>500000</v>
@@ -14056,13 +14082,13 @@
         <v>1200000</v>
       </c>
       <c r="J10" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P10">
         <v>201</v>
@@ -14071,27 +14097,27 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="30.75">
       <c r="A11" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="C11" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D11" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G11">
         <v>-500000</v>
@@ -14103,13 +14129,13 @@
         <v>1200000</v>
       </c>
       <c r="J11" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P11">
         <v>400</v>
@@ -14118,27 +14144,27 @@
         <v>0</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="30.75">
       <c r="A12" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C12" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D12" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G12">
         <v>100000</v>
@@ -14150,13 +14176,13 @@
         <v>900000</v>
       </c>
       <c r="J12" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P12">
         <v>201</v>
@@ -14165,27 +14191,27 @@
         <v>1</v>
       </c>
       <c r="R12" s="14" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="30.75">
+      <c r="A13" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>1042</v>
-      </c>
       <c r="F13" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G13">
         <v>5000000</v>
@@ -14197,13 +14223,13 @@
         <v>10000000</v>
       </c>
       <c r="J13" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P13">
         <v>201</v>
@@ -14212,27 +14238,27 @@
         <v>1</v>
       </c>
       <c r="R13" s="14" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="30.75">
+      <c r="A14" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>1045</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>1042</v>
-      </c>
       <c r="F14" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -14244,13 +14270,13 @@
         <v>900000</v>
       </c>
       <c r="J14" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P14">
         <v>400</v>
@@ -14259,27 +14285,27 @@
         <v>0</v>
       </c>
       <c r="R14" s="14" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15">
       <c r="A15" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="C15" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D15" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G15">
         <v>300000</v>
@@ -14291,13 +14317,13 @@
         <v>900000</v>
       </c>
       <c r="J15" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P15">
         <v>201</v>
@@ -14306,27 +14332,27 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="30.75">
       <c r="A16" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="C16" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D16" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G16">
         <v>-300000</v>
@@ -14338,13 +14364,13 @@
         <v>900000</v>
       </c>
       <c r="J16" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P16">
         <v>400</v>
@@ -14353,27 +14379,27 @@
         <v>0</v>
       </c>
       <c r="R16" s="14" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15">
       <c r="A17" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C17" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D17" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G17">
         <v>50000</v>
@@ -14385,13 +14411,13 @@
         <v>1000000</v>
       </c>
       <c r="J17" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P17">
         <v>201</v>
@@ -14400,27 +14426,27 @@
         <v>1</v>
       </c>
       <c r="R17" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15">
+      <c r="A18" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F18" s="14" t="s">
         <v>1060</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>1056</v>
       </c>
       <c r="G18">
         <v>2000000</v>
@@ -14432,13 +14458,13 @@
         <v>10000000</v>
       </c>
       <c r="J18" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P18">
         <v>201</v>
@@ -14447,27 +14473,27 @@
         <v>1</v>
       </c>
       <c r="R18" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15">
+      <c r="A19" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>1060</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>1056</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -14479,13 +14505,13 @@
         <v>1000000</v>
       </c>
       <c r="J19" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P19">
         <v>400</v>
@@ -14494,27 +14520,27 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15">
       <c r="A20" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="C20" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D20" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G20">
         <v>150000</v>
@@ -14526,13 +14552,13 @@
         <v>1000000</v>
       </c>
       <c r="J20" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P20">
         <v>201</v>
@@ -14541,27 +14567,27 @@
         <v>1</v>
       </c>
       <c r="R20" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15">
+      <c r="A21" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>1060</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>1056</v>
       </c>
       <c r="G21">
         <v>-150000</v>
@@ -14573,13 +14599,13 @@
         <v>1000000</v>
       </c>
       <c r="J21" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P21">
         <v>400</v>
@@ -14588,27 +14614,27 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15">
       <c r="A22" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="C22" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D22" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G22">
         <v>100000</v>
@@ -14620,13 +14646,13 @@
         <v>800000</v>
       </c>
       <c r="J22" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P22">
         <v>201</v>
@@ -14635,27 +14661,27 @@
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15">
       <c r="A23" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="C23" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D23" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G23">
         <v>7500000</v>
@@ -14667,13 +14693,13 @@
         <v>80000000</v>
       </c>
       <c r="J23" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P23">
         <v>201</v>
@@ -14682,27 +14708,27 @@
         <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15">
       <c r="A24" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="C24" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D24" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -14714,13 +14740,13 @@
         <v>800000</v>
       </c>
       <c r="J24" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P24">
         <v>400</v>
@@ -14729,27 +14755,27 @@
         <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15">
       <c r="A25" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="C25" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D25" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G25">
         <v>200000</v>
@@ -14761,13 +14787,13 @@
         <v>800000</v>
       </c>
       <c r="J25" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P25">
         <v>201</v>
@@ -14776,27 +14802,27 @@
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15">
       <c r="A26" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="C26" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D26" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G26">
         <v>-200000</v>
@@ -14808,13 +14834,13 @@
         <v>800000</v>
       </c>
       <c r="J26" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P26">
         <v>400</v>
@@ -14823,27 +14849,27 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15">
       <c r="A27" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="C27" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D27" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G27">
         <v>500000</v>
@@ -14855,13 +14881,13 @@
         <v>10000000</v>
       </c>
       <c r="J27" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P27">
         <v>201</v>
@@ -14870,27 +14896,27 @@
         <v>1</v>
       </c>
       <c r="R27" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15">
       <c r="A28" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C28" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D28" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G28">
         <v>500000</v>
@@ -14902,13 +14928,13 @@
         <v>10000000</v>
       </c>
       <c r="J28" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P28">
         <v>201</v>
@@ -14917,27 +14943,27 @@
         <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15">
       <c r="A29" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="C29" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D29" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G29">
         <v>500000</v>
@@ -14949,13 +14975,13 @@
         <v>10000000</v>
       </c>
       <c r="J29" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P29">
         <v>400</v>
@@ -14964,27 +14990,27 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15">
       <c r="A30" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C30" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D30" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G30">
         <v>500000</v>
@@ -14996,13 +15022,13 @@
         <v>10000000</v>
       </c>
       <c r="J30" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P30">
         <v>201</v>
@@ -15011,27 +15037,27 @@
         <v>1</v>
       </c>
       <c r="R30" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15">
       <c r="A31" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="C31" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D31" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G31">
         <v>500000</v>
@@ -15043,13 +15069,13 @@
         <v>10000000</v>
       </c>
       <c r="J31" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P31">
         <v>400</v>
@@ -15058,27 +15084,27 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15">
       <c r="A32" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="C32" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D32" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G32">
         <v>500000</v>
@@ -15090,13 +15116,13 @@
         <v>10000000</v>
       </c>
       <c r="J32" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
       <c r="N32" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P32">
         <v>400</v>
@@ -15105,27 +15131,27 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15">
       <c r="A33" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="B33" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="C33" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D33" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E33" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F33" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G33">
         <v>500000</v>
@@ -15137,13 +15163,13 @@
         <v>10000000</v>
       </c>
       <c r="J33" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
       <c r="N33" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P33">
         <v>400</v>
@@ -15152,27 +15178,27 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="15">
       <c r="A34" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="B34" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="C34" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D34" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E34" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F34" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G34">
         <v>300000</v>
@@ -15184,13 +15210,13 @@
         <v>10000000</v>
       </c>
       <c r="J34" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
       <c r="N34" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P34">
         <v>201</v>
@@ -15199,27 +15225,27 @@
         <v>1</v>
       </c>
       <c r="R34" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15">
       <c r="A35" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="B35" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="C35" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D35" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E35" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F35" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G35">
         <v>300000</v>
@@ -15231,13 +15257,13 @@
         <v>10000000</v>
       </c>
       <c r="J35" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P35">
         <v>201</v>
@@ -15246,27 +15272,27 @@
         <v>1</v>
       </c>
       <c r="R35" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="15">
       <c r="A36" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="B36" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="C36" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D36" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E36" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F36" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G36">
         <v>300000</v>
@@ -15278,13 +15304,13 @@
         <v>10000000</v>
       </c>
       <c r="J36" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P36">
         <v>400</v>
@@ -15293,27 +15319,27 @@
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="15">
       <c r="A37" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="B37" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="C37" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D37" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E37" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F37" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G37">
         <v>300000</v>
@@ -15325,13 +15351,13 @@
         <v>10000000</v>
       </c>
       <c r="J37" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
       <c r="N37" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P37">
         <v>201</v>
@@ -15340,27 +15366,27 @@
         <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15">
       <c r="A38" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="B38" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="C38" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D38" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E38" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F38" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G38">
         <v>300000</v>
@@ -15372,13 +15398,13 @@
         <v>10000000</v>
       </c>
       <c r="J38" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
       <c r="N38" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P38">
         <v>400</v>
@@ -15387,27 +15413,27 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="15">
       <c r="A39" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="B39" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="C39" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D39" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E39" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F39" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G39">
         <v>300000</v>
@@ -15419,13 +15445,13 @@
         <v>10000000</v>
       </c>
       <c r="J39" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
       <c r="N39" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P39">
         <v>400</v>
@@ -15434,27 +15460,27 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15">
       <c r="A40" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="B40" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="C40" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D40" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E40" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F40" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G40">
         <v>300000</v>
@@ -15466,13 +15492,13 @@
         <v>10000000</v>
       </c>
       <c r="J40" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P40">
         <v>400</v>
@@ -15481,27 +15507,27 @@
         <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="15">
       <c r="A41" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="B41" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="C41" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D41" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E41" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F41" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G41">
         <v>50000</v>
@@ -15513,13 +15539,13 @@
         <v>10000000</v>
       </c>
       <c r="J41" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P41">
         <v>201</v>
@@ -15528,27 +15554,27 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="15">
+      <c r="A42" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F42" t="s">
         <v>1060</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F42" t="s">
-        <v>1056</v>
       </c>
       <c r="G42">
         <v>50000</v>
@@ -15560,13 +15586,13 @@
         <v>10000000</v>
       </c>
       <c r="J42" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M42">
         <v>0</v>
       </c>
       <c r="N42" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P42">
         <v>201</v>
@@ -15575,27 +15601,27 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15">
+      <c r="A43" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F43" t="s">
         <v>1060</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1056</v>
       </c>
       <c r="G43">
         <v>50000</v>
@@ -15607,13 +15633,13 @@
         <v>10000000</v>
       </c>
       <c r="J43" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M43">
         <v>0</v>
       </c>
       <c r="N43" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P43">
         <v>400</v>
@@ -15622,27 +15648,27 @@
         <v>0</v>
       </c>
       <c r="R43" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15">
       <c r="A44" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="B44" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="C44" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D44" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E44" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F44" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G44">
         <v>50000</v>
@@ -15654,13 +15680,13 @@
         <v>10000000</v>
       </c>
       <c r="J44" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P44">
         <v>201</v>
@@ -15669,27 +15695,27 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="15">
+      <c r="A45" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F45" t="s">
         <v>1060</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F45" t="s">
-        <v>1056</v>
       </c>
       <c r="G45">
         <v>50000</v>
@@ -15701,13 +15727,13 @@
         <v>10000000</v>
       </c>
       <c r="J45" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M45">
         <v>0</v>
       </c>
       <c r="N45" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P45">
         <v>400</v>
@@ -15716,27 +15742,27 @@
         <v>0</v>
       </c>
       <c r="R45" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="15">
       <c r="A46" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="B46" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="C46" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D46" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E46" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F46" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G46">
         <v>50000</v>
@@ -15748,13 +15774,13 @@
         <v>10000000</v>
       </c>
       <c r="J46" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
       <c r="N46" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P46">
         <v>400</v>
@@ -15763,27 +15789,27 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="15">
       <c r="A47" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="B47" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="C47" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D47" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E47" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F47" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G47">
         <v>50000</v>
@@ -15795,13 +15821,13 @@
         <v>10000000</v>
       </c>
       <c r="J47" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
       <c r="N47" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P47">
         <v>400</v>
@@ -15810,27 +15836,27 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="15">
       <c r="A48" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="B48" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="C48" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D48" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E48" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F48" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G48">
         <v>100000</v>
@@ -15842,13 +15868,13 @@
         <v>10000000</v>
       </c>
       <c r="J48" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M48">
         <v>0</v>
       </c>
       <c r="N48" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P48">
         <v>201</v>
@@ -15857,27 +15883,27 @@
         <v>1</v>
       </c>
       <c r="R48" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="15">
       <c r="A49" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="B49" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="C49" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D49" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E49" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F49" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G49">
         <v>100000</v>
@@ -15889,13 +15915,13 @@
         <v>10000000</v>
       </c>
       <c r="J49" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P49">
         <v>201</v>
@@ -15904,27 +15930,27 @@
         <v>1</v>
       </c>
       <c r="R49" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15">
       <c r="A50" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="B50" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="C50" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D50" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E50" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F50" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G50">
         <v>100000</v>
@@ -15936,13 +15962,13 @@
         <v>10000000</v>
       </c>
       <c r="J50" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
       <c r="N50" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P50">
         <v>400</v>
@@ -15951,27 +15977,27 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15">
       <c r="A51" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="B51" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="C51" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D51" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E51" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F51" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G51">
         <v>100000</v>
@@ -15983,13 +16009,13 @@
         <v>10000000</v>
       </c>
       <c r="J51" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M51">
         <v>0</v>
       </c>
       <c r="N51" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P51">
         <v>201</v>
@@ -15998,27 +16024,27 @@
         <v>1</v>
       </c>
       <c r="R51" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15">
       <c r="A52" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="B52" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="C52" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D52" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E52" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F52" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G52">
         <v>100000</v>
@@ -16030,13 +16056,13 @@
         <v>10000000</v>
       </c>
       <c r="J52" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M52">
         <v>0</v>
       </c>
       <c r="N52" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P52">
         <v>400</v>
@@ -16045,27 +16071,27 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="15">
       <c r="A53" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="B53" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="C53" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D53" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E53" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F53" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G53">
         <v>100000</v>
@@ -16077,13 +16103,13 @@
         <v>10000000</v>
       </c>
       <c r="J53" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P53">
         <v>400</v>
@@ -16092,27 +16118,27 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15">
       <c r="A54" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="B54" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="C54" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D54" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E54" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F54" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G54">
         <v>100000</v>
@@ -16124,13 +16150,13 @@
         <v>10000000</v>
       </c>
       <c r="J54" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M54">
         <v>0</v>
       </c>
       <c r="N54" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P54">
         <v>400</v>
@@ -16139,27 +16165,27 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="15">
       <c r="A55" t="s">
-        <v>1187</v>
+        <v>1164</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>1188</v>
+        <v>1165</v>
       </c>
       <c r="C55" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D55" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G55">
         <v>400000</v>
@@ -16171,13 +16197,13 @@
         <v>1200000</v>
       </c>
       <c r="J55" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P55">
         <v>400</v>
@@ -16186,27 +16212,27 @@
         <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="15">
       <c r="A56" t="s">
-        <v>1189</v>
+        <v>1167</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>1203</v>
+        <v>1168</v>
       </c>
       <c r="C56" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D56" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G56">
         <v>30000000</v>
@@ -16218,13 +16244,13 @@
         <v>1200000</v>
       </c>
       <c r="J56" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M56">
         <v>0</v>
       </c>
       <c r="N56" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P56">
         <v>400</v>
@@ -16233,27 +16259,27 @@
         <v>0</v>
       </c>
       <c r="R56" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="30.75">
       <c r="A57" t="s">
-        <v>1190</v>
+        <v>1170</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>1191</v>
+        <v>1171</v>
       </c>
       <c r="C57" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D57" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G57">
         <v>5100000</v>
@@ -16265,13 +16291,13 @@
         <v>10000000</v>
       </c>
       <c r="J57" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M57">
         <v>0</v>
       </c>
       <c r="N57" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P57">
         <v>400</v>
@@ -16280,27 +16306,27 @@
         <v>0</v>
       </c>
       <c r="R57" s="14" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="30.75">
       <c r="A58" t="s">
-        <v>1193</v>
+        <v>1173</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>1192</v>
+        <v>1174</v>
       </c>
       <c r="C58" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D58" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G58">
         <v>95000</v>
@@ -16312,13 +16338,13 @@
         <v>10000000</v>
       </c>
       <c r="J58" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M58">
         <v>0</v>
       </c>
       <c r="N58" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P58">
         <v>400</v>
@@ -16327,27 +16353,27 @@
         <v>0</v>
       </c>
       <c r="R58" s="14" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="15">
       <c r="A59" t="s">
-        <v>1194</v>
+        <v>1176</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>1197</v>
+        <v>1177</v>
       </c>
       <c r="C59" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D59" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G59">
         <v>45000</v>
@@ -16359,13 +16385,13 @@
         <v>10000000</v>
       </c>
       <c r="J59" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
       <c r="N59" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P59">
         <v>400</v>
@@ -16374,27 +16400,27 @@
         <v>0</v>
       </c>
       <c r="R59" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="15">
       <c r="A60" t="s">
-        <v>1195</v>
+        <v>1179</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>1198</v>
+        <v>1180</v>
       </c>
       <c r="C60" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D60" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G60">
         <v>2100000</v>
@@ -16406,13 +16432,13 @@
         <v>10000000</v>
       </c>
       <c r="J60" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
       <c r="N60" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P60">
         <v>400</v>
@@ -16421,27 +16447,27 @@
         <v>0</v>
       </c>
       <c r="R60" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="15">
       <c r="A61" t="s">
-        <v>1196</v>
+        <v>1182</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>1199</v>
+        <v>1183</v>
       </c>
       <c r="C61" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D61" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G61">
         <v>95000</v>
@@ -16453,13 +16479,13 @@
         <v>10000000</v>
       </c>
       <c r="J61" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M61">
         <v>0</v>
       </c>
       <c r="N61" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P61">
         <v>400</v>
@@ -16468,27 +16494,27 @@
         <v>0</v>
       </c>
       <c r="R61" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="30.75">
       <c r="A62" t="s">
-        <v>1201</v>
+        <v>1185</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>1200</v>
+        <v>1186</v>
       </c>
       <c r="C62" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D62" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G62">
         <v>8000000</v>
@@ -16500,13 +16526,13 @@
         <v>10000000</v>
       </c>
       <c r="J62" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62" s="14" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P62">
         <v>400</v>
@@ -16515,27 +16541,227 @@
         <v>0</v>
       </c>
       <c r="R62" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E63" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G63">
+        <v>500000.75</v>
+      </c>
+      <c r="H63">
+        <v>60</v>
+      </c>
+      <c r="I63">
+        <v>1200000</v>
+      </c>
+      <c r="J63" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>1048</v>
+      </c>
+      <c r="P63">
+        <v>400</v>
+      </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G64">
+        <v>300000.5</v>
+      </c>
+      <c r="H64">
+        <v>36</v>
+      </c>
+      <c r="I64">
+        <v>900000</v>
+      </c>
+      <c r="J64" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>5000</v>
+      </c>
+      <c r="N64" t="s">
+        <v>1048</v>
+      </c>
+      <c r="P64">
+        <v>400</v>
+      </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G65">
+        <v>150000.25</v>
+      </c>
+      <c r="H65">
+        <v>24</v>
+      </c>
+      <c r="I65">
+        <v>1000000</v>
+      </c>
+      <c r="J65" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65">
+        <v>2000</v>
+      </c>
+      <c r="N65" t="s">
+        <v>1048</v>
+      </c>
+      <c r="P65">
+        <v>400</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>0</v>
+      </c>
+      <c r="R65" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G66">
+        <v>200000.99</v>
+      </c>
+      <c r="H66">
+        <v>48</v>
+      </c>
+      <c r="I66">
+        <v>800000</v>
+      </c>
+      <c r="J66" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>3000</v>
+      </c>
+      <c r="N66" t="s">
+        <v>1048</v>
+      </c>
+      <c r="P66">
+        <v>400</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
       <c r="A75" t="s">
-        <v>1226</v>
+        <v>1196</v>
       </c>
       <c r="B75" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="C75" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D75" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="E75" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F75" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G75">
         <v>500000</v>
@@ -16547,7 +16773,7 @@
         <v>1200000</v>
       </c>
       <c r="J75" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -16556,7 +16782,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P75">
         <v>200</v>
@@ -16565,27 +16791,27 @@
         <v>1</v>
       </c>
       <c r="R75" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
       <c r="A76" t="s">
-        <v>1227</v>
+        <v>1200</v>
       </c>
       <c r="B76" t="s">
-        <v>1228</v>
+        <v>1201</v>
       </c>
       <c r="C76" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D76" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="E76" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F76" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G76">
         <v>500000</v>
@@ -16597,7 +16823,7 @@
         <v>1200000</v>
       </c>
       <c r="J76" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L76">
         <v>3</v>
@@ -16606,7 +16832,7 @@
         <v>0</v>
       </c>
       <c r="N76" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P76">
         <v>200</v>
@@ -16615,27 +16841,27 @@
         <v>1</v>
       </c>
       <c r="R76" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77" t="s">
-        <v>1229</v>
+        <v>1202</v>
       </c>
       <c r="B77" t="s">
-        <v>1230</v>
+        <v>1203</v>
       </c>
       <c r="C77" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D77" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="E77" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F77" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G77">
         <v>500000</v>
@@ -16647,10 +16873,10 @@
         <v>1200000</v>
       </c>
       <c r="J77" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="K77" t="s">
-        <v>1231</v>
+        <v>1204</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -16659,7 +16885,7 @@
         <v>0</v>
       </c>
       <c r="N77" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P77">
         <v>400</v>
@@ -16668,27 +16894,27 @@
         <v>0</v>
       </c>
       <c r="R77" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78" t="s">
-        <v>1232</v>
+        <v>1205</v>
       </c>
       <c r="B78" t="s">
-        <v>1233</v>
+        <v>1206</v>
       </c>
       <c r="C78" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D78" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="E78" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F78" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G78">
         <v>500000</v>
@@ -16700,10 +16926,10 @@
         <v>1200000</v>
       </c>
       <c r="J78" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="K78" t="s">
-        <v>1186</v>
+        <v>1207</v>
       </c>
       <c r="L78">
         <v>1</v>
@@ -16712,7 +16938,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P78">
         <v>400</v>
@@ -16721,27 +16947,27 @@
         <v>0</v>
       </c>
       <c r="R78" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79" t="s">
-        <v>1234</v>
+        <v>1209</v>
       </c>
       <c r="B79" t="s">
-        <v>1235</v>
+        <v>1210</v>
       </c>
       <c r="C79" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D79" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="E79" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F79" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G79">
         <v>500000</v>
@@ -16753,10 +16979,10 @@
         <v>1200000</v>
       </c>
       <c r="J79" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="K79" t="s">
-        <v>1236</v>
+        <v>1211</v>
       </c>
       <c r="L79">
         <v>2</v>
@@ -16765,7 +16991,7 @@
         <v>0</v>
       </c>
       <c r="N79" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P79">
         <v>400</v>
@@ -16774,27 +17000,27 @@
         <v>0</v>
       </c>
       <c r="R79" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80" t="s">
-        <v>1237</v>
+        <v>1212</v>
       </c>
       <c r="B80" t="s">
-        <v>1238</v>
+        <v>1213</v>
       </c>
       <c r="C80" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D80" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="E80" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F80" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G80">
         <v>500000</v>
@@ -16806,7 +17032,7 @@
         <v>1200000</v>
       </c>
       <c r="J80" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L80">
         <v>13</v>
@@ -16815,7 +17041,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P80">
         <v>400</v>
@@ -16824,13 +17050,13 @@
         <v>0</v>
       </c>
       <c r="R80" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19">
       <c r="F87" s="14"/>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -16851,24 +17077,24 @@
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19">
       <c r="A90" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B90" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C90" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D90" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="E90" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F90" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G90">
         <v>500000</v>
@@ -16880,7 +17106,7 @@
         <v>1200000</v>
       </c>
       <c r="J90" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -16889,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P90">
         <v>200</v>
@@ -16898,27 +17124,27 @@
         <v>1</v>
       </c>
       <c r="R90" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19">
       <c r="A91" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="B91" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C91" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D91" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E91" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F91" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G91">
         <v>500000</v>
@@ -16930,7 +17156,7 @@
         <v>1200000</v>
       </c>
       <c r="J91" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L91">
         <v>1</v>
@@ -16939,7 +17165,7 @@
         <v>0</v>
       </c>
       <c r="N91" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P91">
         <v>201</v>
@@ -16948,27 +17174,27 @@
         <v>1</v>
       </c>
       <c r="R91" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19">
       <c r="A92" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="B92" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C92" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D92" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E92" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F92" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="G92">
         <v>100000</v>
@@ -16980,7 +17206,7 @@
         <v>1200000</v>
       </c>
       <c r="J92" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L92">
         <v>1</v>
@@ -16989,7 +17215,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P92">
         <v>201</v>
@@ -16998,27 +17224,27 @@
         <v>1</v>
       </c>
       <c r="R92" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19">
       <c r="A93" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="B93" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="C93" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D93" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E93" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F93" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="G93">
         <v>100000</v>
@@ -17030,7 +17256,7 @@
         <v>1200000</v>
       </c>
       <c r="J93" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -17039,7 +17265,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P93">
         <v>201</v>
@@ -17048,27 +17274,27 @@
         <v>1</v>
       </c>
       <c r="R93" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19">
+      <c r="A94" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E94" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F94" t="s">
         <v>1060</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>1222</v>
-      </c>
-      <c r="B94" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D94" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E94" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F94" t="s">
-        <v>1056</v>
       </c>
       <c r="G94">
         <v>100000</v>
@@ -17080,7 +17306,7 @@
         <v>1200000</v>
       </c>
       <c r="J94" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L94">
         <v>1</v>
@@ -17089,7 +17315,7 @@
         <v>0</v>
       </c>
       <c r="N94" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="P94">
         <v>500</v>
@@ -17098,27 +17324,27 @@
         <v>0</v>
       </c>
       <c r="R94" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" ht="30.75">
       <c r="A95" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D95" t="s">
         <v>1217</v>
       </c>
-      <c r="B95" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D95" t="s">
-        <v>1212</v>
-      </c>
       <c r="E95" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F95" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G95">
         <v>500000</v>
@@ -17130,7 +17356,7 @@
         <v>1200000</v>
       </c>
       <c r="J95" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="L95">
         <v>1</v>
@@ -17138,8 +17364,8 @@
       <c r="M95">
         <v>0</v>
       </c>
-      <c r="N95" t="s">
-        <v>1242</v>
+      <c r="N95" s="14" t="s">
+        <v>1229</v>
       </c>
       <c r="P95">
         <v>400</v>
@@ -17148,10 +17374,10 @@
         <v>0</v>
       </c>
       <c r="R95" t="s">
-        <v>1225</v>
-      </c>
-      <c r="S95" t="s">
-        <v>1242</v>
+        <v>1230</v>
+      </c>
+      <c r="S95" s="14" t="s">
+        <v>1229</v>
       </c>
     </row>
   </sheetData>
@@ -17163,61 +17389,61 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:M23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="7" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="7" width="29.7109375" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="19.6640625" customWidth="1"/>
-    <col min="10" max="10" width="25.5546875" customWidth="1"/>
-    <col min="11" max="11" width="24.88671875" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="11" width="24.85546875" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" s="2" customFormat="1">
       <c r="A2" s="42" t="s">
         <v>180</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>1159</v>
+        <v>1231</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>1160</v>
+        <v>1232</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>1161</v>
+        <v>1233</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1162</v>
+        <v>1234</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>1163</v>
+        <v>1235</v>
       </c>
       <c r="G2" s="43" t="s">
         <v>185</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>1164</v>
+        <v>1236</v>
       </c>
       <c r="I2" s="43" t="s">
-        <v>1165</v>
+        <v>1237</v>
       </c>
       <c r="J2" s="43" t="s">
-        <v>1166</v>
+        <v>1238</v>
       </c>
       <c r="K2" s="43" t="s">
-        <v>1167</v>
+        <v>1239</v>
       </c>
       <c r="L2" s="43" t="s">
         <v>188</v>
       </c>
       <c r="M2" s="43" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="34"/>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -17232,7 +17458,7 @@
       <c r="L3" s="34"/>
       <c r="M3" s="34"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13">
       <c r="A4" s="34"/>
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
@@ -17247,7 +17473,7 @@
       <c r="L4" s="34"/>
       <c r="M4" s="34"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
@@ -17262,7 +17488,7 @@
       <c r="L5" s="34"/>
       <c r="M5" s="34"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="A6" s="34"/>
       <c r="B6" s="34"/>
       <c r="C6" s="34"/>
@@ -17277,7 +17503,7 @@
       <c r="L6" s="34"/>
       <c r="M6" s="34"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13">
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
@@ -17292,7 +17518,7 @@
       <c r="L7" s="34"/>
       <c r="M7" s="34"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="A8" s="34"/>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
@@ -17307,7 +17533,7 @@
       <c r="L8" s="34"/>
       <c r="M8" s="34"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="A9" s="34"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -17322,7 +17548,7 @@
       <c r="L9" s="34"/>
       <c r="M9" s="34"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13">
       <c r="A10" s="34"/>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
@@ -17337,7 +17563,7 @@
       <c r="L10" s="34"/>
       <c r="M10" s="34"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="A11" s="34"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -17352,7 +17578,7 @@
       <c r="L11" s="34"/>
       <c r="M11" s="34"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13">
       <c r="A12" s="34"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -17367,7 +17593,7 @@
       <c r="L12" s="34"/>
       <c r="M12" s="34"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13">
       <c r="A13" s="34"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -17382,7 +17608,7 @@
       <c r="L13" s="34"/>
       <c r="M13" s="34"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13">
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -17397,7 +17623,7 @@
       <c r="L14" s="34"/>
       <c r="M14" s="34"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -17412,7 +17638,7 @@
       <c r="L15" s="34"/>
       <c r="M15" s="34"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13">
       <c r="A16" s="34"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
@@ -17427,7 +17653,7 @@
       <c r="L16" s="34"/>
       <c r="M16" s="34"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="34"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -17442,7 +17668,7 @@
       <c r="L17" s="34"/>
       <c r="M17" s="34"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="34"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -17457,7 +17683,7 @@
       <c r="L18" s="34"/>
       <c r="M18" s="34"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="34"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -17472,7 +17698,7 @@
       <c r="L19" s="34"/>
       <c r="M19" s="34"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="34"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -17487,7 +17713,7 @@
       <c r="L20" s="34"/>
       <c r="M20" s="34"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="34"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -17502,7 +17728,7 @@
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="34"/>
       <c r="B22" s="34"/>
       <c r="C22" s="34"/>
@@ -17517,7 +17743,7 @@
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="34"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -17540,17 +17766,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:F20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" customWidth="1"/>
-    <col min="3" max="3" width="52.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="44" t="s">
         <v>180</v>
       </c>
@@ -17558,19 +17784,19 @@
         <v>5</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>1169</v>
+        <v>1241</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>1170</v>
+        <v>1242</v>
       </c>
       <c r="E2" s="45" t="s">
-        <v>1171</v>
+        <v>1243</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="34"/>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -17578,7 +17804,7 @@
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="34"/>
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
@@ -17586,7 +17812,7 @@
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
@@ -17594,7 +17820,7 @@
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="34"/>
       <c r="B6" s="34"/>
       <c r="C6" s="34"/>
@@ -17602,7 +17828,7 @@
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
@@ -17610,7 +17836,7 @@
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="34"/>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
@@ -17618,7 +17844,7 @@
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="34"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -17626,7 +17852,7 @@
       <c r="E9" s="34"/>
       <c r="F9" s="34"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="34"/>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
@@ -17634,7 +17860,7 @@
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="34"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -17642,7 +17868,7 @@
       <c r="E11" s="34"/>
       <c r="F11" s="34"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="34"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -17650,7 +17876,7 @@
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="34"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -17658,7 +17884,7 @@
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -17666,7 +17892,7 @@
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -17674,7 +17900,7 @@
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="34"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
@@ -17682,7 +17908,7 @@
       <c r="E16" s="34"/>
       <c r="F16" s="34"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="34"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -17690,7 +17916,7 @@
       <c r="E17" s="34"/>
       <c r="F17" s="34"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="34"/>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -17698,7 +17924,7 @@
       <c r="E18" s="34"/>
       <c r="F18" s="34"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="34"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -17706,7 +17932,7 @@
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="34"/>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
@@ -17722,42 +17948,42 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="49.44140625" customWidth="1"/>
-    <col min="3" max="3" width="54.33203125" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
-    <col min="5" max="5" width="32.6640625" customWidth="1"/>
-    <col min="6" max="6" width="29.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="49.42578125" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:6" ht="24.95" customHeight="1">
       <c r="C1" s="3" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="46" t="s">
-        <v>1174</v>
+        <v>1246</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>1175</v>
+        <v>1247</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>1176</v>
+        <v>1248</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>1177</v>
+        <v>1249</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>1178</v>
+        <v>1250</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="34"/>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -17765,7 +17991,7 @@
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="34"/>
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
@@ -17773,7 +17999,7 @@
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
@@ -17781,7 +18007,7 @@
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="34"/>
       <c r="B6" s="34"/>
       <c r="C6" s="34"/>
@@ -17789,7 +18015,7 @@
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
@@ -17797,7 +18023,7 @@
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="34"/>
       <c r="B8" s="34"/>
       <c r="C8" s="34"/>
@@ -17805,7 +18031,7 @@
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="34"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -17813,7 +18039,7 @@
       <c r="E9" s="34"/>
       <c r="F9" s="34"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="34"/>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
@@ -17821,7 +18047,7 @@
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="34"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -17829,7 +18055,7 @@
       <c r="E11" s="34"/>
       <c r="F11" s="34"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="34"/>
       <c r="B12" s="34"/>
       <c r="C12" s="34"/>
@@ -17837,7 +18063,7 @@
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="34"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -17845,7 +18071,7 @@
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -17853,7 +18079,7 @@
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -17861,7 +18087,7 @@
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="34"/>
       <c r="B16" s="34"/>
       <c r="C16" s="34"/>
